--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,6 +54,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -507,7 +575,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -582,7 +650,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -657,7 +725,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -732,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -807,7 +875,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -882,7 +950,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -957,7 +1025,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1100,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1175,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1250,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1328,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1406,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1484,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1562,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1640,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1718,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1796,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1874,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1952,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1962,7 +2030,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2108,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2186,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2264,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2342,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2420,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2498,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2576,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2654,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2732,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2810,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2888,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2966,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2976,7 +3044,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3122,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3200,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3278,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3356,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3434,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3512,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3590,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3668,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3746,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3824,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3902,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3980,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3990,7 +4058,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4136,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4214,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4292,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4370,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4448,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4526,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4604,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4682,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4760,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4838,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4916,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4994,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5072,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5150,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5228,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5306,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5384,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5462,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5469,7 +5537,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5612,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5690,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5765,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5840,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5915,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5990,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6068,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6143,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6218,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6293,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6368,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6446,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6521,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6596,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6671,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6746,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6824,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6902,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6980,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -6990,7 +7058,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7136,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7214,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7292,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7370,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7448,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7526,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7604,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7682,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7692,7 +7760,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7838,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7916,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7994,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8004,7 +8072,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8150,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8160,7 +8228,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8306,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8384,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8462,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8540,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8618,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8696,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8774,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8852,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8930,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -8940,7 +9008,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9086,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9164,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9242,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9320,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9398,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9408,7 +9476,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9486,7 +9554,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9564,7 +9632,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9710,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9788,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9798,7 +9866,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9876,7 +9944,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -9954,7 +10022,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10100,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10178,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10188,7 +10256,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10334,7 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10412,7 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10422,7 +10490,7 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10568,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10578,7 +10646,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10721,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10796,7 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10871,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10878,7 +10946,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -10953,7 +11021,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11096,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11103,7 +11171,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11178,7 +11246,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11253,7 +11321,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11396,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11471,7 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11478,7 +11546,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11621,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11696,7 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11771,7 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11846,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11921,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11996,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12071,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12078,7 +12146,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12153,7 +12221,7 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12228,7 +12296,7 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12303,7 +12371,7 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12378,7 +12446,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12521,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12528,7 +12596,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12671,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12678,7 +12746,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12753,7 +12821,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12828,7 +12896,7 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12903,7 +12971,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -12978,7 +13046,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13121,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13128,7 +13196,7 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13203,7 +13271,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13346,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13353,7 +13421,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13496,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13503,7 +13571,7 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13578,7 +13646,7 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13653,7 +13721,7 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13731,7 +13799,7 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13809,7 +13877,7 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13887,7 +13955,7 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -13965,7 +14033,7 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14043,7 +14111,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14121,7 +14189,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14267,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14277,7 +14345,7 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14423,7 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14433,7 +14501,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14511,7 +14579,7 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14589,7 +14657,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14667,7 +14735,7 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14813,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14823,7 +14891,7 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14969,7 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -14979,7 +15047,7 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15057,7 +15125,7 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15135,7 +15203,7 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15213,7 +15281,7 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15291,7 +15359,7 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15369,7 +15437,7 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15447,7 +15515,7 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15525,7 +15593,7 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15671,7 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15746,7 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15753,7 +15821,7 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15828,7 +15896,7 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15903,7 +15971,7 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -15978,7 +16046,7 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16121,7 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16128,7 +16196,7 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16203,7 +16271,7 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16278,7 +16346,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16353,7 +16421,7 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16428,7 +16496,7 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16503,7 +16571,7 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16646,7 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16653,7 +16721,7 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16728,7 +16796,7 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16803,7 +16871,7 @@
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16878,7 +16946,7 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -16953,7 +17021,7 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17028,7 +17096,7 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17103,7 +17171,7 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17178,7 +17246,7 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17253,7 +17321,7 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17328,7 +17396,7 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17403,7 +17471,7 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17478,7 +17546,7 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17621,7 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17628,7 +17696,7 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17703,7 +17771,7 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17778,7 +17846,7 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17921,7 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -17928,7 +17996,7 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18006,7 +18074,7 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18081,7 +18149,7 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18159,7 +18227,7 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18237,7 +18305,7 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18315,7 +18383,7 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18393,7 +18461,7 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18539,7 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18549,7 +18617,7 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18627,7 +18695,7 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18705,7 +18773,7 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18851,7 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18861,7 +18929,7 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -18939,7 +19007,7 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19017,7 +19085,7 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19095,7 +19163,7 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19173,7 +19241,7 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19251,7 +19319,7 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19329,7 +19397,7 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19407,7 +19475,7 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19485,7 +19553,7 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19563,7 +19631,7 @@
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19641,7 +19709,7 @@
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19719,7 +19787,7 @@
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19865,7 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19875,7 +19943,7 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -19953,7 +20021,7 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20031,7 +20099,7 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20106,7 +20174,7 @@
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20181,7 +20249,7 @@
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20259,7 +20327,7 @@
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20405,7 @@
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20415,7 +20483,7 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20493,7 +20561,7 @@
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20571,7 +20639,7 @@
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20649,7 +20717,7 @@
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20792,7 @@
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20774,7 +20842,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -597,7 +612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -674,7 +689,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -751,7 +766,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -828,7 +843,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -905,7 +920,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -982,7 +997,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1059,7 +1074,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1136,7 +1151,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1213,7 +1228,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1290,7 +1305,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1367,7 +1382,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1400,7 +1415,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="N17" s="7" t="n">
         <v>1253300</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1446,7 +1461,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1479,7 +1494,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="N18" s="7" t="n">
         <v>1301600</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -1525,7 +1540,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1558,7 +1573,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="N19" s="7" t="n">
         <v>1511000</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -1604,7 +1619,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1637,7 +1652,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="N20" s="7" t="n">
         <v>1765900</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -1683,7 +1698,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1716,7 +1731,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="N21" s="7" t="n">
         <v>1981500</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -1762,7 +1777,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1795,7 +1810,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N22" s="4" t="n">
+      <c r="N22" s="7" t="n">
         <v>2355200</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -1841,7 +1856,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1874,7 +1889,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="N23" s="7" t="n">
         <v>2708400</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -1920,7 +1935,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1953,7 +1968,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="N24" s="7" t="n">
         <v>3500600</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -1999,7 +2014,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2032,7 +2047,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="N25" s="7" t="n">
         <v>4042700</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2078,7 +2093,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2111,7 +2126,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N26" s="4" t="n">
+      <c r="N26" s="7" t="n">
         <v>4771700</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
@@ -2157,7 +2172,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2190,7 +2205,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="N27" s="7" t="n">
         <v>5133300</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2236,7 +2251,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2269,7 +2284,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="N28" s="7" t="n">
         <v>5147000</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -2315,7 +2330,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2348,7 +2363,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N29" s="4" t="n">
+      <c r="N29" s="7" t="n">
         <v>5667200</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -2394,7 +2409,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2427,7 +2442,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N30" s="4" t="n">
+      <c r="N30" s="7" t="n">
         <v>5000200</v>
       </c>
       <c r="O30" s="4" t="inlineStr">
@@ -2473,7 +2488,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2506,7 +2521,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N31" s="4" t="n">
+      <c r="N31" s="7" t="n">
         <v>4570800</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -2552,7 +2567,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2585,7 +2600,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N32" s="4" t="n">
+      <c r="N32" s="7" t="n">
         <v>4966500</v>
       </c>
       <c r="O32" s="4" t="inlineStr">
@@ -2631,7 +2646,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2664,7 +2679,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N33" s="4" t="n">
+      <c r="N33" s="7" t="n">
         <v>5790900</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -2710,7 +2725,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2743,7 +2758,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="N34" s="7" t="n">
         <v>6454100</v>
       </c>
       <c r="O34" s="4" t="inlineStr">
@@ -2789,7 +2804,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2822,7 +2837,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N35" s="4" t="n">
+      <c r="N35" s="7" t="n">
         <v>8383800</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -2868,7 +2883,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2901,7 +2916,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N36" s="4" t="n">
+      <c r="N36" s="7" t="n">
         <v>10098800</v>
       </c>
       <c r="O36" s="4" t="inlineStr">
@@ -2947,7 +2962,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2980,7 +2995,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N37" s="4" t="n">
+      <c r="N37" s="7" t="n">
         <v>6846800</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -3026,7 +3041,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3059,7 +3074,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N38" s="4" t="n">
+      <c r="N38" s="7" t="n">
         <v>6795200</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
@@ -3105,7 +3120,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3138,7 +3153,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N39" s="4" t="n">
+      <c r="N39" s="7" t="n">
         <v>7149400</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3184,7 +3199,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3217,7 +3232,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N40" s="4" t="n">
+      <c r="N40" s="7" t="n">
         <v>6813900</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
@@ -3263,7 +3278,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3296,7 +3311,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N41" s="4" t="n">
+      <c r="N41" s="7" t="n">
         <v>5266800</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -3342,7 +3357,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3375,7 +3390,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="N42" s="7" t="n">
         <v>4445000</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
@@ -3421,7 +3436,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3454,7 +3469,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N43" s="4" t="n">
+      <c r="N43" s="7" t="n">
         <v>4487400</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
@@ -3500,7 +3515,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3533,7 +3548,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N44" s="4" t="n">
+      <c r="N44" s="7" t="n">
         <v>4020300</v>
       </c>
       <c r="O44" s="4" t="inlineStr">
@@ -3579,7 +3594,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3612,7 +3627,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N45" s="4" t="n">
+      <c r="N45" s="7" t="n">
         <v>3736600</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
@@ -3658,7 +3673,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3691,7 +3706,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N46" s="4" t="n">
+      <c r="N46" s="7" t="n">
         <v>4690000</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
@@ -3737,7 +3752,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3770,7 +3785,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N47" s="4" t="n">
+      <c r="N47" s="7" t="n">
         <v>4295000</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -3816,7 +3831,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3849,7 +3864,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N48" s="4" t="n">
+      <c r="N48" s="7" t="n">
         <v>9452434</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
@@ -3895,7 +3910,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3928,7 +3943,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N49" s="4" t="n">
+      <c r="N49" s="7" t="n">
         <v>6369455</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -3974,7 +3989,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -4007,7 +4022,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="N50" s="7" t="n">
         <v>3889929</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
@@ -4053,7 +4068,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4086,7 +4101,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N51" s="4" t="n">
+      <c r="N51" s="7" t="n">
         <v>4943887</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -4132,7 +4147,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4165,7 +4180,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="N52" s="7" t="n">
         <v>5043028</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
@@ -4211,7 +4226,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4244,7 +4259,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N53" s="4" t="n">
+      <c r="N53" s="7" t="n">
         <v>5225573</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4290,7 +4305,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4323,7 +4338,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N54" s="4" t="n">
+      <c r="N54" s="7" t="n">
         <v>5495292</v>
       </c>
       <c r="O54" s="4" t="inlineStr">
@@ -4369,7 +4384,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4402,7 +4417,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N55" s="4" t="n">
+      <c r="N55" s="7" t="n">
         <v>5766973</v>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -4448,7 +4463,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4481,7 +4496,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N56" s="4" t="n">
+      <c r="N56" s="7" t="n">
         <v>5121009</v>
       </c>
       <c r="O56" s="4" t="inlineStr">
@@ -4527,7 +4542,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4560,7 +4575,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N57" s="4" t="n">
+      <c r="N57" s="7" t="n">
         <v>6428163</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -4606,7 +4621,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4639,7 +4654,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N58" s="4" t="n">
+      <c r="N58" s="8" t="n">
         <v>7728281.25393288</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
@@ -4685,7 +4700,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4718,7 +4733,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N59" s="4" t="n">
+      <c r="N59" s="8" t="n">
         <v>7738509.64544939</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
@@ -4764,7 +4779,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4797,7 +4812,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N60" s="4" t="n">
+      <c r="N60" s="8" t="n">
         <v>6866780.59935996</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
@@ -4843,7 +4858,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4876,7 +4891,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N61" s="4" t="n">
+      <c r="N61" s="8" t="n">
         <v>7888722.39935996</v>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -4922,7 +4937,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4955,7 +4970,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N62" s="4" t="n">
+      <c r="N62" s="7" t="n">
         <v>7086072</v>
       </c>
       <c r="O62" s="4" t="inlineStr">
@@ -5001,7 +5016,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5034,7 +5049,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N63" s="4" t="n">
+      <c r="N63" s="7" t="n">
         <v>6025475</v>
       </c>
       <c r="O63" s="4" t="inlineStr">
@@ -5080,7 +5095,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5113,7 +5128,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N64" s="4" t="n">
+      <c r="N64" s="7" t="n">
         <v>4209158</v>
       </c>
       <c r="O64" s="4" t="inlineStr">
@@ -5159,7 +5174,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5192,7 +5207,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N65" s="4" t="n">
+      <c r="N65" s="7" t="n">
         <v>2217407</v>
       </c>
       <c r="O65" s="4" t="inlineStr">
@@ -5238,7 +5253,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5271,7 +5286,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N66" s="4" t="n">
+      <c r="N66" s="7" t="n">
         <v>1516839</v>
       </c>
       <c r="O66" s="4" t="inlineStr">
@@ -5317,7 +5332,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="G67" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5350,7 +5365,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N67" s="4" t="n">
+      <c r="N67" s="7" t="n">
         <v>283524</v>
       </c>
       <c r="O67" s="4" t="inlineStr">
@@ -5396,7 +5411,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5429,7 +5444,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N68" s="4" t="n">
+      <c r="N68" s="7" t="n">
         <v>265276</v>
       </c>
       <c r="O68" s="4" t="inlineStr">
@@ -5475,7 +5490,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5508,7 +5523,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N69" s="4" t="n">
+      <c r="N69" s="7" t="n">
         <v>1373948</v>
       </c>
       <c r="O69" s="4" t="inlineStr">
@@ -5554,7 +5569,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5587,7 +5602,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N70" s="4" t="n">
+      <c r="N70" s="7" t="n">
         <v>1783667</v>
       </c>
       <c r="O70" s="4" t="inlineStr">
@@ -5633,7 +5648,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5710,7 +5725,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5787,7 +5802,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5820,7 +5835,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N73" s="4" t="n">
+      <c r="N73" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O73" s="4" t="inlineStr">
@@ -5866,7 +5881,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -5943,7 +5958,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -6020,7 +6035,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6097,7 +6112,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6174,7 +6189,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6207,7 +6222,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N78" s="4" t="n">
+      <c r="N78" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O78" s="4" t="inlineStr">
@@ -6253,7 +6268,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6330,7 +6345,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6407,7 +6422,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6484,7 +6499,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G82" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6561,7 +6576,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6594,7 +6609,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N83" s="4" t="n">
+      <c r="N83" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O83" s="4" t="inlineStr">
@@ -6640,7 +6655,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6717,7 +6732,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6794,7 +6809,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="G86" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -6871,7 +6886,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -6948,7 +6963,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -6981,7 +6996,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N88" s="4" t="n">
+      <c r="N88" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O88" s="4" t="inlineStr">
@@ -7027,7 +7042,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="G89" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7060,7 +7075,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N89" s="4" t="n">
+      <c r="N89" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -7106,7 +7121,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="G90" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7139,7 +7154,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N90" s="4" t="n">
+      <c r="N90" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O90" s="4" t="inlineStr">
@@ -7185,7 +7200,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G91" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7218,7 +7233,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N91" s="4" t="n">
+      <c r="N91" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O91" s="4" t="inlineStr">
@@ -7264,7 +7279,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="G92" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7297,7 +7312,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N92" s="4" t="n">
+      <c r="N92" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O92" s="4" t="inlineStr">
@@ -7343,7 +7358,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7376,7 +7391,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N93" s="4" t="n">
+      <c r="N93" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O93" s="4" t="inlineStr">
@@ -7422,7 +7437,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7455,7 +7470,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N94" s="4" t="n">
+      <c r="N94" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O94" s="4" t="inlineStr">
@@ -7501,7 +7516,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="G95" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7534,7 +7549,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N95" s="4" t="n">
+      <c r="N95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O95" s="4" t="inlineStr">
@@ -7580,7 +7595,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="G96" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7613,7 +7628,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N96" s="4" t="n">
+      <c r="N96" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O96" s="4" t="inlineStr">
@@ -7659,7 +7674,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7692,7 +7707,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N97" s="4" t="n">
+      <c r="N97" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O97" s="4" t="inlineStr">
@@ -7738,7 +7753,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -7771,7 +7786,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N98" s="4" t="n">
+      <c r="N98" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O98" s="4" t="inlineStr">
@@ -7817,7 +7832,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -7850,7 +7865,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N99" s="4" t="n">
+      <c r="N99" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O99" s="4" t="inlineStr">
@@ -7896,7 +7911,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -7929,7 +7944,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N100" s="4" t="n">
+      <c r="N100" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O100" s="4" t="inlineStr">
@@ -7975,7 +7990,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="G101" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -8008,7 +8023,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N101" s="4" t="n">
+      <c r="N101" s="8" t="n">
         <v>0.009574076000000001</v>
       </c>
       <c r="O101" s="4" t="inlineStr">
@@ -8054,7 +8069,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="G102" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8087,7 +8102,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N102" s="4" t="n">
+      <c r="N102" s="8" t="n">
         <v>0.019117739</v>
       </c>
       <c r="O102" s="4" t="inlineStr">
@@ -8133,7 +8148,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8166,7 +8181,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N103" s="4" t="n">
+      <c r="N103" s="8" t="n">
         <v>0.037578645</v>
       </c>
       <c r="O103" s="4" t="inlineStr">
@@ -8212,7 +8227,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="G104" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8245,7 +8260,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N104" s="4" t="n">
+      <c r="N104" s="8" t="n">
         <v>0.08207171100000001</v>
       </c>
       <c r="O104" s="4" t="inlineStr">
@@ -8291,7 +8306,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8324,7 +8339,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N105" s="4" t="n">
+      <c r="N105" s="8" t="n">
         <v>0.379508456</v>
       </c>
       <c r="O105" s="4" t="inlineStr">
@@ -8370,7 +8385,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8403,7 +8418,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N106" s="4" t="n">
+      <c r="N106" s="8" t="n">
         <v>0.862455779</v>
       </c>
       <c r="O106" s="4" t="inlineStr">
@@ -8449,7 +8464,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="G107" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8482,7 +8497,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N107" s="4" t="n">
+      <c r="N107" s="8" t="n">
         <v>1.474065254</v>
       </c>
       <c r="O107" s="4" t="inlineStr">
@@ -8528,7 +8543,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n">
+      <c r="G108" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8561,7 +8576,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N108" s="4" t="n">
+      <c r="N108" s="8" t="n">
         <v>1.826547139</v>
       </c>
       <c r="O108" s="4" t="inlineStr">
@@ -8607,7 +8622,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="G109" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8640,7 +8655,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N109" s="4" t="n">
+      <c r="N109" s="8" t="n">
         <v>2.577074097</v>
       </c>
       <c r="O109" s="4" t="inlineStr">
@@ -8686,7 +8701,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n">
+      <c r="G110" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -8719,7 +8734,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N110" s="4" t="n">
+      <c r="N110" s="8" t="n">
         <v>4.652836296</v>
       </c>
       <c r="O110" s="4" t="inlineStr">
@@ -8765,7 +8780,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="G111" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -8798,7 +8813,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N111" s="4" t="n">
+      <c r="N111" s="8" t="n">
         <v>8.550767856</v>
       </c>
       <c r="O111" s="4" t="inlineStr">
@@ -8844,7 +8859,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="G112" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -8877,7 +8892,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N112" s="4" t="n">
+      <c r="N112" s="8" t="n">
         <v>15.79146876</v>
       </c>
       <c r="O112" s="4" t="inlineStr">
@@ -8923,7 +8938,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n">
+      <c r="G113" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -8956,7 +8971,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N113" s="4" t="n">
+      <c r="N113" s="8" t="n">
         <v>22.2091444151412</v>
       </c>
       <c r="O113" s="4" t="inlineStr">
@@ -9002,7 +9017,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n">
+      <c r="G114" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -9035,7 +9050,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N114" s="4" t="n">
+      <c r="N114" s="8" t="n">
         <v>25.9111457593823</v>
       </c>
       <c r="O114" s="4" t="inlineStr">
@@ -9081,7 +9096,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="G115" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9114,7 +9129,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N115" s="4" t="n">
+      <c r="N115" s="8" t="n">
         <v>25.7193686771621</v>
       </c>
       <c r="O115" s="4" t="inlineStr">
@@ -9160,7 +9175,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n">
+      <c r="G116" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9193,7 +9208,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N116" s="4" t="n">
+      <c r="N116" s="8" t="n">
         <v>27.0930423911324</v>
       </c>
       <c r="O116" s="4" t="inlineStr">
@@ -9239,7 +9254,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="4" t="n">
+      <c r="G117" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9272,7 +9287,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N117" s="4" t="n">
+      <c r="N117" s="8" t="n">
         <v>31.9692942191133</v>
       </c>
       <c r="O117" s="4" t="inlineStr">
@@ -9318,7 +9333,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n">
+      <c r="G118" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9351,7 +9366,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N118" s="4" t="n">
+      <c r="N118" s="8" t="n">
         <v>46.6505354851398</v>
       </c>
       <c r="O118" s="4" t="inlineStr">
@@ -9397,7 +9412,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n">
+      <c r="G119" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9430,7 +9445,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N119" s="4" t="n">
+      <c r="N119" s="8" t="n">
         <v>69.0162817672167</v>
       </c>
       <c r="O119" s="4" t="inlineStr">
@@ -9476,7 +9491,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n">
+      <c r="G120" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9509,7 +9524,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N120" s="4" t="n">
+      <c r="N120" s="8" t="n">
         <v>86.15074784905531</v>
       </c>
       <c r="O120" s="4" t="inlineStr">
@@ -9555,7 +9570,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n">
+      <c r="G121" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9588,7 +9603,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N121" s="4" t="n">
+      <c r="N121" s="8" t="n">
         <v>97.7210881589364</v>
       </c>
       <c r="O121" s="4" t="inlineStr">
@@ -9634,7 +9649,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n">
+      <c r="G122" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9667,7 +9682,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N122" s="4" t="n">
+      <c r="N122" s="8" t="n">
         <v>98.89329523166261</v>
       </c>
       <c r="O122" s="4" t="inlineStr">
@@ -9713,7 +9728,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n">
+      <c r="G123" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -9746,7 +9761,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N123" s="4" t="n">
+      <c r="N123" s="8" t="n">
         <v>96.76199725951049</v>
       </c>
       <c r="O123" s="4" t="inlineStr">
@@ -9792,7 +9807,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n">
+      <c r="G124" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -9825,7 +9840,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N124" s="4" t="n">
+      <c r="N124" s="8" t="n">
         <v>98.6184338835709</v>
       </c>
       <c r="O124" s="4" t="inlineStr">
@@ -9871,7 +9886,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n">
+      <c r="G125" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -9904,7 +9919,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N125" s="4" t="n">
+      <c r="N125" s="8" t="n">
         <v>103.435247267139</v>
       </c>
       <c r="O125" s="4" t="inlineStr">
@@ -9950,7 +9965,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n">
+      <c r="G126" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -9983,7 +9998,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N126" s="4" t="n">
+      <c r="N126" s="8" t="n">
         <v>103.28923003251</v>
       </c>
       <c r="O126" s="4" t="inlineStr">
@@ -10029,7 +10044,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="G127" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10062,7 +10077,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N127" s="4" t="n">
+      <c r="N127" s="8" t="n">
         <v>100.905474597326</v>
       </c>
       <c r="O127" s="4" t="inlineStr">
@@ -10108,7 +10123,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="4" t="n">
+      <c r="G128" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10141,7 +10156,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N128" s="4" t="n">
+      <c r="N128" s="8" t="n">
         <v>95.15779304043321</v>
       </c>
       <c r="O128" s="4" t="inlineStr">
@@ -10187,7 +10202,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="4" t="n">
+      <c r="G129" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10220,7 +10235,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N129" s="4" t="n">
+      <c r="N129" s="8" t="n">
         <v>89.713138519105</v>
       </c>
       <c r="O129" s="4" t="inlineStr">
@@ -10266,7 +10281,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="4" t="n">
+      <c r="G130" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10299,7 +10314,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N130" s="4" t="n">
+      <c r="N130" s="8" t="n">
         <v>80.1355411817503</v>
       </c>
       <c r="O130" s="4" t="inlineStr">
@@ -10345,7 +10360,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n">
+      <c r="G131" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10378,7 +10393,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N131" s="4" t="n">
+      <c r="N131" s="8" t="n">
         <v>69.54996230490541</v>
       </c>
       <c r="O131" s="4" t="inlineStr">
@@ -10424,7 +10439,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n">
+      <c r="G132" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10457,7 +10472,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N132" s="4" t="n">
+      <c r="N132" s="8" t="n">
         <v>63.8474442929871</v>
       </c>
       <c r="O132" s="4" t="inlineStr">
@@ -10503,7 +10518,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n">
+      <c r="G133" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10536,7 +10551,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N133" s="4" t="n">
+      <c r="N133" s="8" t="n">
         <v>58.1625657953324</v>
       </c>
       <c r="O133" s="4" t="inlineStr">
@@ -10582,7 +10597,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="4" t="n">
+      <c r="G134" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10615,7 +10630,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N134" s="4" t="n">
+      <c r="N134" s="8" t="n">
         <v>60.2344883065715</v>
       </c>
       <c r="O134" s="4" t="inlineStr">
@@ -10661,7 +10676,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n">
+      <c r="G135" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -10694,7 +10709,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N135" s="4" t="n">
+      <c r="N135" s="8" t="n">
         <v>66.4667731210739</v>
       </c>
       <c r="O135" s="4" t="inlineStr">
@@ -10740,7 +10755,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n">
+      <c r="G136" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -10773,7 +10788,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N136" s="4" t="n">
+      <c r="N136" s="8" t="n">
         <v>70.2197325918151</v>
       </c>
       <c r="O136" s="4" t="inlineStr">
@@ -10819,7 +10834,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n">
+      <c r="G137" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -10852,7 +10867,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N137" s="4" t="n">
+      <c r="N137" s="8" t="n">
         <v>71.00759172250289</v>
       </c>
       <c r="O137" s="4" t="inlineStr">
@@ -10898,7 +10913,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n">
+      <c r="G138" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -10975,7 +10990,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n">
+      <c r="G139" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -11052,7 +11067,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n">
+      <c r="G140" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -11129,7 +11144,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n">
+      <c r="G141" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -11206,7 +11221,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G142" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -11283,7 +11298,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n">
+      <c r="G143" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -11360,7 +11375,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
+      <c r="G144" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -11437,7 +11452,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="4" t="n">
+      <c r="G145" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -11514,7 +11529,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n">
+      <c r="G146" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -11591,7 +11606,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n">
+      <c r="G147" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -11668,7 +11683,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G148" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -11745,7 +11760,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G149" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -11822,7 +11837,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n">
+      <c r="G150" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -11899,7 +11914,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n">
+      <c r="G151" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -11976,7 +11991,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="4" t="n">
+      <c r="G152" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -12053,7 +12068,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="4" t="n">
+      <c r="G153" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -12130,7 +12145,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="4" t="n">
+      <c r="G154" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -12207,7 +12222,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n">
+      <c r="G155" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -12284,7 +12299,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="4" t="n">
+      <c r="G156" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -12361,7 +12376,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n">
+      <c r="G157" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
@@ -12438,7 +12453,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n">
+      <c r="G158" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
@@ -12515,7 +12530,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="4" t="n">
+      <c r="G159" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
@@ -12592,7 +12607,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="4" t="n">
+      <c r="G160" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -12669,7 +12684,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n">
+      <c r="G161" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -12746,7 +12761,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n">
+      <c r="G162" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -12823,7 +12838,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n">
+      <c r="G163" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -12900,7 +12915,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n">
+      <c r="G164" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -12977,7 +12992,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n">
+      <c r="G165" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -13054,7 +13069,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G166" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -13131,7 +13146,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n">
+      <c r="G167" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -13208,7 +13223,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n">
+      <c r="G168" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -13285,7 +13300,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n">
+      <c r="G169" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -13362,7 +13377,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n">
+      <c r="G170" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -13439,7 +13454,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n">
+      <c r="G171" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -13516,7 +13531,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n">
+      <c r="G172" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -13593,7 +13608,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n">
+      <c r="G173" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -13670,7 +13685,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n">
+      <c r="G174" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -13747,7 +13762,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n">
+      <c r="G175" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -13824,7 +13839,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
+      <c r="G176" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -13901,7 +13916,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n">
+      <c r="G177" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -13978,7 +13993,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
+      <c r="G178" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -14055,7 +14070,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n">
+      <c r="G179" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -14088,7 +14103,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N179" s="4" t="n">
+      <c r="N179" s="8" t="n">
         <v>0.0182372620084196</v>
       </c>
       <c r="O179" s="4" t="inlineStr">
@@ -14134,7 +14149,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n">
+      <c r="G180" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -14167,7 +14182,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N180" s="4" t="n">
+      <c r="N180" s="8" t="n">
         <v>0.146661787014387</v>
       </c>
       <c r="O180" s="4" t="inlineStr">
@@ -14213,7 +14228,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n">
+      <c r="G181" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -14246,7 +14261,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N181" s="4" t="n">
+      <c r="N181" s="8" t="n">
         <v>0.307249610202931</v>
       </c>
       <c r="O181" s="4" t="inlineStr">
@@ -14292,7 +14307,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n">
+      <c r="G182" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -14325,7 +14340,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N182" s="4" t="n">
+      <c r="N182" s="8" t="n">
         <v>0.451853172687301</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
@@ -14371,7 +14386,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n">
+      <c r="G183" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -14404,7 +14419,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N183" s="4" t="n">
+      <c r="N183" s="8" t="n">
         <v>0.798034595558425</v>
       </c>
       <c r="O183" s="4" t="inlineStr">
@@ -14450,7 +14465,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n">
+      <c r="G184" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -14483,7 +14498,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N184" s="4" t="n">
+      <c r="N184" s="8" t="n">
         <v>1.32980141271847</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
@@ -14529,7 +14544,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n">
+      <c r="G185" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -14562,7 +14577,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N185" s="4" t="n">
+      <c r="N185" s="8" t="n">
         <v>1.97478127020455</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
@@ -14608,7 +14623,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
+      <c r="G186" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -14641,7 +14656,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N186" s="4" t="n">
+      <c r="N186" s="8" t="n">
         <v>3.10246568790753</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
@@ -14687,7 +14702,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n">
+      <c r="G187" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -14720,7 +14735,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N187" s="4" t="n">
+      <c r="N187" s="8" t="n">
         <v>3.97495217742432</v>
       </c>
       <c r="O187" s="4" t="inlineStr">
@@ -14766,7 +14781,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n">
+      <c r="G188" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -14799,7 +14814,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N188" s="4" t="n">
+      <c r="N188" s="8" t="n">
         <v>4.92838214157542</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
@@ -14845,7 +14860,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n">
+      <c r="G189" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -14878,7 +14893,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N189" s="4" t="n">
+      <c r="N189" s="8" t="n">
         <v>5.80665024566429</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
@@ -14924,7 +14939,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n">
+      <c r="G190" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -14957,7 +14972,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N190" s="4" t="n">
+      <c r="N190" s="8" t="n">
         <v>6.22108895422792</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
@@ -15003,7 +15018,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n">
+      <c r="G191" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -15036,7 +15051,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N191" s="4" t="n">
+      <c r="N191" s="8" t="n">
         <v>6.89152396038334</v>
       </c>
       <c r="O191" s="4" t="inlineStr">
@@ -15082,7 +15097,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n">
+      <c r="G192" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -15115,7 +15130,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N192" s="4" t="n">
+      <c r="N192" s="8" t="n">
         <v>7.4666228138768</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
@@ -15161,7 +15176,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n">
+      <c r="G193" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -15194,7 +15209,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N193" s="4" t="n">
+      <c r="N193" s="8" t="n">
         <v>7.9330889563685</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
@@ -15240,7 +15255,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n">
+      <c r="G194" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -15273,7 +15288,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N194" s="4" t="n">
+      <c r="N194" s="8" t="n">
         <v>8.470319132888591</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
@@ -15319,7 +15334,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n">
+      <c r="G195" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -15352,7 +15367,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N195" s="4" t="n">
+      <c r="N195" s="8" t="n">
         <v>8.496440193826119</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
@@ -15398,7 +15413,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
+      <c r="G196" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -15431,7 +15446,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N196" s="4" t="n">
+      <c r="N196" s="8" t="n">
         <v>8.531985740834481</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
@@ -15477,7 +15492,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n">
+      <c r="G197" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -15510,7 +15525,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N197" s="4" t="n">
+      <c r="N197" s="8" t="n">
         <v>8.737968501447551</v>
       </c>
       <c r="O197" s="4" t="inlineStr">
@@ -15556,7 +15571,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="4" t="n">
+      <c r="G198" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -15589,7 +15604,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N198" s="4" t="n">
+      <c r="N198" s="8" t="n">
         <v>8.850374340428321</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
@@ -15635,7 +15650,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="4" t="n">
+      <c r="G199" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -15668,7 +15683,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N199" s="4" t="n">
+      <c r="N199" s="8" t="n">
         <v>9.00606477756336</v>
       </c>
       <c r="O199" s="4" t="inlineStr">
@@ -15714,7 +15729,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="4" t="n">
+      <c r="G200" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -15747,7 +15762,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N200" s="4" t="n">
+      <c r="N200" s="8" t="n">
         <v>9.2424360147272</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
@@ -15793,7 +15808,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="4" t="n">
+      <c r="G201" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -15826,7 +15841,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N201" s="4" t="n">
+      <c r="N201" s="8" t="n">
         <v>9.580361433872881</v>
       </c>
       <c r="O201" s="4" t="inlineStr">
@@ -15872,7 +15887,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="4" t="n">
+      <c r="G202" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -15905,7 +15920,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N202" s="4" t="n">
+      <c r="N202" s="8" t="n">
         <v>10.638053537183</v>
       </c>
       <c r="O202" s="4" t="inlineStr">
@@ -15951,7 +15966,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="4" t="n">
+      <c r="G203" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
@@ -15984,7 +15999,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N203" s="4" t="n">
+      <c r="N203" s="8" t="n">
         <v>12.9446636524427</v>
       </c>
       <c r="O203" s="4" t="inlineStr">
@@ -16030,7 +16045,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="4" t="n">
+      <c r="G204" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -16107,7 +16122,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="4" t="n">
+      <c r="G205" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -16184,7 +16199,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="4" t="n">
+      <c r="G206" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -16261,7 +16276,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="4" t="n">
+      <c r="G207" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
@@ -16338,7 +16353,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="4" t="n">
+      <c r="G208" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -16415,7 +16430,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="4" t="n">
+      <c r="G209" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -16492,7 +16507,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="4" t="n">
+      <c r="G210" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -16569,7 +16584,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="4" t="n">
+      <c r="G211" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -16646,7 +16661,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="4" t="n">
+      <c r="G212" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -16723,7 +16738,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="4" t="n">
+      <c r="G213" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -16800,7 +16815,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="4" t="n">
+      <c r="G214" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -16877,7 +16892,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="4" t="n">
+      <c r="G215" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -16954,7 +16969,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="4" t="n">
+      <c r="G216" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
@@ -17031,7 +17046,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="4" t="n">
+      <c r="G217" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
@@ -17108,7 +17123,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="4" t="n">
+      <c r="G218" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -17185,7 +17200,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="4" t="n">
+      <c r="G219" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -17262,7 +17277,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="4" t="n">
+      <c r="G220" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -17339,7 +17354,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="4" t="n">
+      <c r="G221" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -17416,7 +17431,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="4" t="n">
+      <c r="G222" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -17493,7 +17508,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="4" t="n">
+      <c r="G223" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -17570,7 +17585,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="4" t="n">
+      <c r="G224" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -17647,7 +17662,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="4" t="n">
+      <c r="G225" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -17724,7 +17739,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="4" t="n">
+      <c r="G226" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -17801,7 +17816,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="4" t="n">
+      <c r="G227" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -17878,7 +17893,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="4" t="n">
+      <c r="G228" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -17955,7 +17970,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="4" t="n">
+      <c r="G229" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
@@ -18032,7 +18047,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="4" t="n">
+      <c r="G230" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -18109,7 +18124,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="4" t="n">
+      <c r="G231" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
@@ -18186,7 +18201,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="4" t="n">
+      <c r="G232" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
@@ -18263,7 +18278,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="4" t="n">
+      <c r="G233" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
@@ -18340,7 +18355,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="4" t="n">
+      <c r="G234" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
@@ -18417,7 +18432,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="4" t="n">
+      <c r="G235" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -18450,7 +18465,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N235" s="4" t="n">
+      <c r="N235" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O235" s="4" t="inlineStr">
@@ -18496,7 +18511,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="4" t="n">
+      <c r="G236" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
@@ -18573,7 +18588,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="4" t="n">
+      <c r="G237" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -18606,7 +18621,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N237" s="4" t="n">
+      <c r="N237" s="8" t="n">
         <v>0.0121</v>
       </c>
       <c r="O237" s="4" t="inlineStr">
@@ -18652,7 +18667,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="4" t="n">
+      <c r="G238" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
@@ -18685,7 +18700,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N238" s="4" t="n">
+      <c r="N238" s="8" t="n">
         <v>0.0416</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
@@ -18731,7 +18746,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="4" t="n">
+      <c r="G239" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
@@ -18764,7 +18779,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N239" s="4" t="n">
+      <c r="N239" s="8" t="n">
         <v>0.0555</v>
       </c>
       <c r="O239" s="4" t="inlineStr">
@@ -18810,7 +18825,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="4" t="n">
+      <c r="G240" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
@@ -18843,7 +18858,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N240" s="4" t="n">
+      <c r="N240" s="8" t="n">
         <v>0.122</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
@@ -18889,7 +18904,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="4" t="n">
+      <c r="G241" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
@@ -18922,7 +18937,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N241" s="4" t="n">
+      <c r="N241" s="8" t="n">
         <v>0.248</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
@@ -18968,7 +18983,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="4" t="n">
+      <c r="G242" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
@@ -19001,7 +19016,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N242" s="4" t="n">
+      <c r="N242" s="8" t="n">
         <v>0.391</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
@@ -19047,7 +19062,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="4" t="n">
+      <c r="G243" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
@@ -19080,7 +19095,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N243" s="4" t="n">
+      <c r="N243" s="8" t="n">
         <v>1.38</v>
       </c>
       <c r="O243" s="4" t="inlineStr">
@@ -19126,7 +19141,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="4" t="n">
+      <c r="G244" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
@@ -19159,7 +19174,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N244" s="4" t="n">
+      <c r="N244" s="8" t="n">
         <v>2.84</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
@@ -19205,7 +19220,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="4" t="n">
+      <c r="G245" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -19238,7 +19253,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N245" s="4" t="n">
+      <c r="N245" s="8" t="n">
         <v>3.3595974645036</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
@@ -19284,7 +19299,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="4" t="n">
+      <c r="G246" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -19317,7 +19332,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N246" s="4" t="n">
+      <c r="N246" s="8" t="n">
         <v>4.63600094778677</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
@@ -19363,7 +19378,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="4" t="n">
+      <c r="G247" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -19396,7 +19411,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N247" s="4" t="n">
+      <c r="N247" s="8" t="n">
         <v>4.91044632720325</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
@@ -19442,7 +19457,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="4" t="n">
+      <c r="G248" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -19475,7 +19490,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N248" s="4" t="n">
+      <c r="N248" s="8" t="n">
         <v>7.49996346522407</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
@@ -19521,7 +19536,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="4" t="n">
+      <c r="G249" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -19554,7 +19569,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N249" s="4" t="n">
+      <c r="N249" s="8" t="n">
         <v>8.40446959241215</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
@@ -19600,7 +19615,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="4" t="n">
+      <c r="G250" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -19633,7 +19648,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N250" s="4" t="n">
+      <c r="N250" s="8" t="n">
         <v>12.5529979098299</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
@@ -19679,7 +19694,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="4" t="n">
+      <c r="G251" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -19712,7 +19727,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N251" s="4" t="n">
+      <c r="N251" s="8" t="n">
         <v>15.2247114771787</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
@@ -19758,7 +19773,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="4" t="n">
+      <c r="G252" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -19791,7 +19806,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N252" s="4" t="n">
+      <c r="N252" s="8" t="n">
         <v>20.83</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
@@ -19837,7 +19852,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="4" t="n">
+      <c r="G253" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -19870,7 +19885,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N253" s="4" t="n">
+      <c r="N253" s="8" t="n">
         <v>25.88</v>
       </c>
       <c r="O253" s="4" t="inlineStr">
@@ -19916,7 +19931,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="4" t="n">
+      <c r="G254" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -19949,7 +19964,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N254" s="4" t="n">
+      <c r="N254" s="8" t="n">
         <v>32.7</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
@@ -19995,7 +20010,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="4" t="n">
+      <c r="G255" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -20028,7 +20043,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N255" s="4" t="n">
+      <c r="N255" s="8" t="n">
         <v>37.37</v>
       </c>
       <c r="O255" s="4" t="inlineStr">
@@ -20074,7 +20089,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="4" t="n">
+      <c r="G256" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
@@ -20107,7 +20122,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N256" s="4" t="n">
+      <c r="N256" s="8" t="n">
         <v>40.22</v>
       </c>
       <c r="O256" s="4" t="inlineStr">
@@ -20153,7 +20168,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="4" t="n">
+      <c r="G257" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
@@ -20186,7 +20201,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N257" s="4" t="n">
+      <c r="N257" s="8" t="n">
         <v>49.0500830729861</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
@@ -20232,7 +20247,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="4" t="n">
+      <c r="G258" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
@@ -20265,7 +20280,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N258" s="4" t="n">
+      <c r="N258" s="8" t="n">
         <v>54.90000153</v>
       </c>
       <c r="O258" s="4" t="inlineStr">
@@ -20311,7 +20326,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="4" t="n">
+      <c r="G259" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
@@ -20344,7 +20359,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N259" s="4" t="n">
+      <c r="N259" s="7" t="n">
         <v>57</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
@@ -20390,7 +20405,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="4" t="n">
+      <c r="G260" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
@@ -20423,7 +20438,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N260" s="4" t="n">
+      <c r="N260" s="7" t="n">
         <v>58</v>
       </c>
       <c r="O260" s="4" t="inlineStr">
@@ -20469,7 +20484,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="4" t="n">
+      <c r="G261" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
@@ -20502,7 +20517,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N261" s="4" t="n">
+      <c r="N261" s="7" t="n">
         <v>60</v>
       </c>
       <c r="O261" s="4" t="inlineStr">
@@ -20548,7 +20563,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="4" t="n">
+      <c r="G262" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
@@ -20625,7 +20640,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="4" t="n">
+      <c r="G263" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
@@ -20702,7 +20717,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="4" t="n">
+      <c r="G264" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
@@ -20735,7 +20750,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N264" s="4" t="n">
+      <c r="N264" s="8" t="n">
         <v>49.05009842</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
@@ -20781,7 +20796,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="4" t="n">
+      <c r="G265" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
@@ -20814,7 +20829,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N265" s="4" t="n">
+      <c r="N265" s="8" t="n">
         <v>72.44110107</v>
       </c>
       <c r="O265" s="4" t="inlineStr">
@@ -20860,7 +20875,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="4" t="n">
+      <c r="G266" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
@@ -20893,7 +20908,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N266" s="4" t="n">
+      <c r="N266" s="8" t="n">
         <v>74.11219788</v>
       </c>
       <c r="O266" s="4" t="inlineStr">
@@ -20939,7 +20954,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="4" t="n">
+      <c r="G267" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
@@ -20972,7 +20987,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N267" s="4" t="n">
+      <c r="N267" s="8" t="n">
         <v>75.82180022999999</v>
       </c>
       <c r="O267" s="4" t="inlineStr">
@@ -21018,7 +21033,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="4" t="n">
+      <c r="G268" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
@@ -21051,7 +21066,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N268" s="4" t="n">
+      <c r="N268" s="8" t="n">
         <v>76.33190155</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
@@ -21097,7 +21112,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="4" t="n">
+      <c r="G269" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
@@ -21130,7 +21145,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N269" s="4" t="n">
+      <c r="N269" s="8" t="n">
         <v>76.67890167</v>
       </c>
       <c r="O269" s="4" t="inlineStr">
@@ -21176,7 +21191,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="4" t="n">
+      <c r="G270" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
@@ -21312,7 +21327,7 @@
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7" t="n">
         <v>4</v>
       </c>
     </row>
@@ -21322,7 +21337,7 @@
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7" t="n">
         <v>264</v>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -82,26 +82,94 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -116,16 +184,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -134,7 +199,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -149,16 +214,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -480,14 +542,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Banco Mundial - Venezuela - Infraestructura y digitalización</t>
+          <t>Banco Mundial - Infraestructura y digitalización</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>World Development Indicators</t>
+          <t>Venezuela</t>
         </is>
       </c>
     </row>
@@ -612,7 +674,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="5" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -653,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -689,7 +751,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="5" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -730,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -766,7 +828,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="5" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -807,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -843,7 +905,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="5" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -884,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -920,7 +982,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="5" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -961,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -997,7 +1059,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="5" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1038,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1074,7 +1136,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="5" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1115,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1151,7 +1213,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="5" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1192,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1228,7 +1290,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="5" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1269,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1305,7 +1367,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="5" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1346,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1382,7 +1444,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="5" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1415,7 +1477,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N17" s="7" t="n">
+      <c r="N17" s="5" t="n">
         <v>1253300</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1425,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1461,7 +1523,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="5" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1494,7 +1556,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N18" s="7" t="n">
+      <c r="N18" s="5" t="n">
         <v>1301600</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -1504,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1540,7 +1602,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="5" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1573,7 +1635,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N19" s="7" t="n">
+      <c r="N19" s="5" t="n">
         <v>1511000</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -1583,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1619,7 +1681,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="5" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1652,7 +1714,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N20" s="7" t="n">
+      <c r="N20" s="5" t="n">
         <v>1765900</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -1662,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1698,7 +1760,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="5" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1731,7 +1793,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N21" s="7" t="n">
+      <c r="N21" s="5" t="n">
         <v>1981500</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -1741,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1777,7 +1839,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="5" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1810,7 +1872,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N22" s="7" t="n">
+      <c r="N22" s="5" t="n">
         <v>2355200</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -1820,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1856,7 +1918,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="5" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1889,7 +1951,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N23" s="7" t="n">
+      <c r="N23" s="5" t="n">
         <v>2708400</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -1899,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -1935,7 +1997,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G24" s="5" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1968,7 +2030,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N24" s="7" t="n">
+      <c r="N24" s="5" t="n">
         <v>3500600</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -1978,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2014,7 +2076,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="G25" s="5" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2047,7 +2109,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N25" s="7" t="n">
+      <c r="N25" s="5" t="n">
         <v>4042700</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2057,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2093,7 +2155,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G26" s="5" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2126,7 +2188,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N26" s="7" t="n">
+      <c r="N26" s="5" t="n">
         <v>4771700</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
@@ -2136,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2172,7 +2234,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="G27" s="5" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2205,7 +2267,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N27" s="7" t="n">
+      <c r="N27" s="5" t="n">
         <v>5133300</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2215,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2251,7 +2313,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="5" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2284,7 +2346,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N28" s="7" t="n">
+      <c r="N28" s="5" t="n">
         <v>5147000</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -2294,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2330,7 +2392,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="G29" s="5" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2363,7 +2425,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N29" s="7" t="n">
+      <c r="N29" s="5" t="n">
         <v>5667200</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -2373,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2409,7 +2471,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G30" s="5" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2442,7 +2504,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N30" s="7" t="n">
+      <c r="N30" s="5" t="n">
         <v>5000200</v>
       </c>
       <c r="O30" s="4" t="inlineStr">
@@ -2452,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2488,7 +2550,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G31" s="5" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2521,7 +2583,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N31" s="7" t="n">
+      <c r="N31" s="5" t="n">
         <v>4570800</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -2531,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2567,7 +2629,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="5" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2600,7 +2662,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N32" s="7" t="n">
+      <c r="N32" s="5" t="n">
         <v>4966500</v>
       </c>
       <c r="O32" s="4" t="inlineStr">
@@ -2610,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2646,7 +2708,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="G33" s="5" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2679,7 +2741,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N33" s="7" t="n">
+      <c r="N33" s="5" t="n">
         <v>5790900</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -2689,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2725,7 +2787,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="5" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2758,7 +2820,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N34" s="7" t="n">
+      <c r="N34" s="5" t="n">
         <v>6454100</v>
       </c>
       <c r="O34" s="4" t="inlineStr">
@@ -2768,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2804,7 +2866,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G35" s="5" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2837,7 +2899,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N35" s="7" t="n">
+      <c r="N35" s="5" t="n">
         <v>8383800</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -2847,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2883,7 +2945,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G36" s="5" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2916,7 +2978,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N36" s="7" t="n">
+      <c r="N36" s="5" t="n">
         <v>10098800</v>
       </c>
       <c r="O36" s="4" t="inlineStr">
@@ -2926,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -2962,7 +3024,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="G37" s="5" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2995,7 +3057,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N37" s="7" t="n">
+      <c r="N37" s="5" t="n">
         <v>6846800</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -3005,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3041,7 +3103,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="G38" s="5" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3074,7 +3136,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N38" s="7" t="n">
+      <c r="N38" s="5" t="n">
         <v>6795200</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
@@ -3084,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3120,7 +3182,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="7" t="n">
+      <c r="G39" s="5" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3153,7 +3215,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N39" s="7" t="n">
+      <c r="N39" s="5" t="n">
         <v>7149400</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3163,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3199,7 +3261,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G40" s="5" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3232,7 +3294,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N40" s="7" t="n">
+      <c r="N40" s="5" t="n">
         <v>6813900</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
@@ -3242,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3278,7 +3340,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="G41" s="5" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3311,7 +3373,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N41" s="7" t="n">
+      <c r="N41" s="5" t="n">
         <v>5266800</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -3321,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3357,7 +3419,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="7" t="n">
+      <c r="G42" s="5" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3390,7 +3452,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N42" s="7" t="n">
+      <c r="N42" s="5" t="n">
         <v>4445000</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
@@ -3400,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3436,7 +3498,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="7" t="n">
+      <c r="G43" s="5" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3469,7 +3531,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N43" s="7" t="n">
+      <c r="N43" s="5" t="n">
         <v>4487400</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
@@ -3479,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3515,7 +3577,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="5" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3548,7 +3610,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N44" s="7" t="n">
+      <c r="N44" s="5" t="n">
         <v>4020300</v>
       </c>
       <c r="O44" s="4" t="inlineStr">
@@ -3558,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3594,7 +3656,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="G45" s="5" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3627,7 +3689,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N45" s="7" t="n">
+      <c r="N45" s="5" t="n">
         <v>3736600</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
@@ -3637,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3673,7 +3735,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="G46" s="5" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3706,7 +3768,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N46" s="7" t="n">
+      <c r="N46" s="5" t="n">
         <v>4690000</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
@@ -3716,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3752,7 +3814,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G47" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3785,7 +3847,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N47" s="7" t="n">
+      <c r="N47" s="5" t="n">
         <v>4295000</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -3795,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3831,7 +3893,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="G48" s="5" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3864,7 +3926,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N48" s="7" t="n">
+      <c r="N48" s="5" t="n">
         <v>9452434</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
@@ -3874,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3910,7 +3972,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="7" t="n">
+      <c r="G49" s="5" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3943,7 +4005,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N49" s="7" t="n">
+      <c r="N49" s="5" t="n">
         <v>6369455</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -3953,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -3989,7 +4051,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="G50" s="5" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -4022,7 +4084,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N50" s="7" t="n">
+      <c r="N50" s="5" t="n">
         <v>3889929</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
@@ -4032,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4068,7 +4130,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="7" t="n">
+      <c r="G51" s="5" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4101,7 +4163,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N51" s="7" t="n">
+      <c r="N51" s="5" t="n">
         <v>4943887</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -4111,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4147,7 +4209,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="7" t="n">
+      <c r="G52" s="5" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4180,7 +4242,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N52" s="7" t="n">
+      <c r="N52" s="5" t="n">
         <v>5043028</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
@@ -4190,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4226,7 +4288,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="7" t="n">
+      <c r="G53" s="5" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4259,7 +4321,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N53" s="7" t="n">
+      <c r="N53" s="5" t="n">
         <v>5225573</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4269,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4305,7 +4367,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="7" t="n">
+      <c r="G54" s="5" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4338,7 +4400,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N54" s="7" t="n">
+      <c r="N54" s="5" t="n">
         <v>5495292</v>
       </c>
       <c r="O54" s="4" t="inlineStr">
@@ -4348,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4384,7 +4446,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="7" t="n">
+      <c r="G55" s="5" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4417,7 +4479,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N55" s="7" t="n">
+      <c r="N55" s="5" t="n">
         <v>5766973</v>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -4427,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4463,7 +4525,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="7" t="n">
+      <c r="G56" s="5" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4496,7 +4558,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N56" s="7" t="n">
+      <c r="N56" s="5" t="n">
         <v>5121009</v>
       </c>
       <c r="O56" s="4" t="inlineStr">
@@ -4506,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4542,7 +4604,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="7" t="n">
+      <c r="G57" s="5" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4575,7 +4637,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N57" s="7" t="n">
+      <c r="N57" s="5" t="n">
         <v>6428163</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -4585,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4621,7 +4683,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="7" t="n">
+      <c r="G58" s="5" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4654,7 +4716,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N58" s="8" t="n">
+      <c r="N58" s="6" t="n">
         <v>7728281.25393288</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
@@ -4664,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4700,7 +4762,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="7" t="n">
+      <c r="G59" s="5" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4733,7 +4795,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N59" s="8" t="n">
+      <c r="N59" s="6" t="n">
         <v>7738509.64544939</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
@@ -4743,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4779,7 +4841,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="7" t="n">
+      <c r="G60" s="5" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4812,7 +4874,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N60" s="8" t="n">
+      <c r="N60" s="6" t="n">
         <v>6866780.59935996</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
@@ -4822,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4858,7 +4920,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="7" t="n">
+      <c r="G61" s="5" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4891,7 +4953,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N61" s="8" t="n">
+      <c r="N61" s="6" t="n">
         <v>7888722.39935996</v>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -4901,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4937,7 +4999,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="7" t="n">
+      <c r="G62" s="5" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4970,7 +5032,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N62" s="7" t="n">
+      <c r="N62" s="5" t="n">
         <v>7086072</v>
       </c>
       <c r="O62" s="4" t="inlineStr">
@@ -4980,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5016,7 +5078,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="7" t="n">
+      <c r="G63" s="5" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5049,7 +5111,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N63" s="7" t="n">
+      <c r="N63" s="5" t="n">
         <v>6025475</v>
       </c>
       <c r="O63" s="4" t="inlineStr">
@@ -5059,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5095,7 +5157,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="7" t="n">
+      <c r="G64" s="5" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5128,7 +5190,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N64" s="7" t="n">
+      <c r="N64" s="5" t="n">
         <v>4209158</v>
       </c>
       <c r="O64" s="4" t="inlineStr">
@@ -5138,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5174,7 +5236,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="G65" s="5" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5207,7 +5269,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N65" s="7" t="n">
+      <c r="N65" s="5" t="n">
         <v>2217407</v>
       </c>
       <c r="O65" s="4" t="inlineStr">
@@ -5217,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5253,7 +5315,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="7" t="n">
+      <c r="G66" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5286,7 +5348,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N66" s="7" t="n">
+      <c r="N66" s="5" t="n">
         <v>1516839</v>
       </c>
       <c r="O66" s="4" t="inlineStr">
@@ -5296,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5332,7 +5394,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="7" t="n">
+      <c r="G67" s="5" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5365,7 +5427,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N67" s="7" t="n">
+      <c r="N67" s="5" t="n">
         <v>283524</v>
       </c>
       <c r="O67" s="4" t="inlineStr">
@@ -5375,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5411,7 +5473,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="7" t="n">
+      <c r="G68" s="5" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5444,7 +5506,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N68" s="7" t="n">
+      <c r="N68" s="5" t="n">
         <v>265276</v>
       </c>
       <c r="O68" s="4" t="inlineStr">
@@ -5454,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5490,7 +5552,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="7" t="n">
+      <c r="G69" s="5" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5523,7 +5585,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N69" s="7" t="n">
+      <c r="N69" s="5" t="n">
         <v>1373948</v>
       </c>
       <c r="O69" s="4" t="inlineStr">
@@ -5533,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5569,7 +5631,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="7" t="n">
+      <c r="G70" s="5" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5602,7 +5664,7 @@
           <t>Pasajeros transportados por vía aérea</t>
         </is>
       </c>
-      <c r="N70" s="7" t="n">
+      <c r="N70" s="5" t="n">
         <v>1783667</v>
       </c>
       <c r="O70" s="4" t="inlineStr">
@@ -5612,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5648,7 +5710,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="7" t="n">
+      <c r="G71" s="5" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5689,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5725,7 +5787,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="7" t="n">
+      <c r="G72" s="5" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5766,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5802,7 +5864,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="7" t="n">
+      <c r="G73" s="5" t="n">
         <v>1960</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5835,7 +5897,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N73" s="7" t="n">
+      <c r="N73" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O73" s="4" t="inlineStr">
@@ -5845,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5881,7 +5943,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="7" t="n">
+      <c r="G74" s="5" t="n">
         <v>1961</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -5922,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5958,7 +6020,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="7" t="n">
+      <c r="G75" s="5" t="n">
         <v>1962</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -5999,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6035,7 +6097,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="7" t="n">
+      <c r="G76" s="5" t="n">
         <v>1963</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6076,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6112,7 +6174,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="7" t="n">
+      <c r="G77" s="5" t="n">
         <v>1964</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6153,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6189,7 +6251,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="7" t="n">
+      <c r="G78" s="5" t="n">
         <v>1965</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6222,7 +6284,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N78" s="7" t="n">
+      <c r="N78" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O78" s="4" t="inlineStr">
@@ -6232,7 +6294,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6268,7 +6330,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="7" t="n">
+      <c r="G79" s="5" t="n">
         <v>1966</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6309,7 +6371,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6345,7 +6407,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="7" t="n">
+      <c r="G80" s="5" t="n">
         <v>1967</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6386,7 +6448,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6422,7 +6484,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="7" t="n">
+      <c r="G81" s="5" t="n">
         <v>1968</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6463,7 +6525,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6499,7 +6561,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="7" t="n">
+      <c r="G82" s="5" t="n">
         <v>1969</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6540,7 +6602,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6576,7 +6638,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="7" t="n">
+      <c r="G83" s="5" t="n">
         <v>1970</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6609,7 +6671,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N83" s="7" t="n">
+      <c r="N83" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O83" s="4" t="inlineStr">
@@ -6619,7 +6681,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6655,7 +6717,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="7" t="n">
+      <c r="G84" s="5" t="n">
         <v>1971</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6696,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6732,7 +6794,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="7" t="n">
+      <c r="G85" s="5" t="n">
         <v>1972</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6773,7 +6835,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6809,7 +6871,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="7" t="n">
+      <c r="G86" s="5" t="n">
         <v>1973</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -6850,7 +6912,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6886,7 +6948,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="7" t="n">
+      <c r="G87" s="5" t="n">
         <v>1974</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -6927,7 +6989,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6963,7 +7025,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="7" t="n">
+      <c r="G88" s="5" t="n">
         <v>1975</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -6996,7 +7058,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N88" s="7" t="n">
+      <c r="N88" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O88" s="4" t="inlineStr">
@@ -7006,7 +7068,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7042,7 +7104,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="7" t="n">
+      <c r="G89" s="5" t="n">
         <v>1976</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7075,7 +7137,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N89" s="7" t="n">
+      <c r="N89" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -7085,7 +7147,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7121,7 +7183,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="7" t="n">
+      <c r="G90" s="5" t="n">
         <v>1977</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7154,7 +7216,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N90" s="7" t="n">
+      <c r="N90" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O90" s="4" t="inlineStr">
@@ -7164,7 +7226,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7200,7 +7262,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="7" t="n">
+      <c r="G91" s="5" t="n">
         <v>1978</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7233,7 +7295,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N91" s="7" t="n">
+      <c r="N91" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O91" s="4" t="inlineStr">
@@ -7243,7 +7305,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7279,7 +7341,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="7" t="n">
+      <c r="G92" s="5" t="n">
         <v>1979</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7312,7 +7374,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N92" s="7" t="n">
+      <c r="N92" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O92" s="4" t="inlineStr">
@@ -7322,7 +7384,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7358,7 +7420,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="7" t="n">
+      <c r="G93" s="5" t="n">
         <v>1980</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7391,7 +7453,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N93" s="7" t="n">
+      <c r="N93" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O93" s="4" t="inlineStr">
@@ -7401,7 +7463,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7437,7 +7499,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="7" t="n">
+      <c r="G94" s="5" t="n">
         <v>1981</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7470,7 +7532,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N94" s="7" t="n">
+      <c r="N94" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O94" s="4" t="inlineStr">
@@ -7480,7 +7542,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7516,7 +7578,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="7" t="n">
+      <c r="G95" s="5" t="n">
         <v>1982</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7549,7 +7611,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N95" s="7" t="n">
+      <c r="N95" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O95" s="4" t="inlineStr">
@@ -7559,7 +7621,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7595,7 +7657,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="7" t="n">
+      <c r="G96" s="5" t="n">
         <v>1983</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7628,7 +7690,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N96" s="7" t="n">
+      <c r="N96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O96" s="4" t="inlineStr">
@@ -7638,7 +7700,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7674,7 +7736,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="7" t="n">
+      <c r="G97" s="5" t="n">
         <v>1984</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7707,7 +7769,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N97" s="7" t="n">
+      <c r="N97" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O97" s="4" t="inlineStr">
@@ -7717,7 +7779,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7753,7 +7815,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="7" t="n">
+      <c r="G98" s="5" t="n">
         <v>1985</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -7786,7 +7848,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N98" s="7" t="n">
+      <c r="N98" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O98" s="4" t="inlineStr">
@@ -7796,7 +7858,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7832,7 +7894,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="7" t="n">
+      <c r="G99" s="5" t="n">
         <v>1986</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -7865,7 +7927,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N99" s="7" t="n">
+      <c r="N99" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O99" s="4" t="inlineStr">
@@ -7875,7 +7937,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7911,7 +7973,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="7" t="n">
+      <c r="G100" s="5" t="n">
         <v>1987</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -7944,7 +8006,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N100" s="7" t="n">
+      <c r="N100" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O100" s="4" t="inlineStr">
@@ -7954,7 +8016,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7990,7 +8052,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="7" t="n">
+      <c r="G101" s="5" t="n">
         <v>1988</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -8023,7 +8085,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N101" s="8" t="n">
+      <c r="N101" s="6" t="n">
         <v>0.009574076000000001</v>
       </c>
       <c r="O101" s="4" t="inlineStr">
@@ -8033,7 +8095,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8069,7 +8131,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="7" t="n">
+      <c r="G102" s="5" t="n">
         <v>1989</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8102,7 +8164,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N102" s="8" t="n">
+      <c r="N102" s="6" t="n">
         <v>0.019117739</v>
       </c>
       <c r="O102" s="4" t="inlineStr">
@@ -8112,7 +8174,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8148,7 +8210,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="7" t="n">
+      <c r="G103" s="5" t="n">
         <v>1990</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8181,7 +8243,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N103" s="8" t="n">
+      <c r="N103" s="6" t="n">
         <v>0.037578645</v>
       </c>
       <c r="O103" s="4" t="inlineStr">
@@ -8191,7 +8253,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8227,7 +8289,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="7" t="n">
+      <c r="G104" s="5" t="n">
         <v>1991</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8260,7 +8322,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N104" s="8" t="n">
+      <c r="N104" s="6" t="n">
         <v>0.08207171100000001</v>
       </c>
       <c r="O104" s="4" t="inlineStr">
@@ -8270,7 +8332,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8306,7 +8368,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="7" t="n">
+      <c r="G105" s="5" t="n">
         <v>1992</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8339,7 +8401,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N105" s="8" t="n">
+      <c r="N105" s="6" t="n">
         <v>0.379508456</v>
       </c>
       <c r="O105" s="4" t="inlineStr">
@@ -8349,7 +8411,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8385,7 +8447,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="7" t="n">
+      <c r="G106" s="5" t="n">
         <v>1993</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8418,7 +8480,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N106" s="8" t="n">
+      <c r="N106" s="6" t="n">
         <v>0.862455779</v>
       </c>
       <c r="O106" s="4" t="inlineStr">
@@ -8428,7 +8490,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8464,7 +8526,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="7" t="n">
+      <c r="G107" s="5" t="n">
         <v>1994</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8497,7 +8559,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N107" s="8" t="n">
+      <c r="N107" s="6" t="n">
         <v>1.474065254</v>
       </c>
       <c r="O107" s="4" t="inlineStr">
@@ -8507,7 +8569,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8543,7 +8605,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="7" t="n">
+      <c r="G108" s="5" t="n">
         <v>1995</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8576,7 +8638,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N108" s="8" t="n">
+      <c r="N108" s="6" t="n">
         <v>1.826547139</v>
       </c>
       <c r="O108" s="4" t="inlineStr">
@@ -8586,7 +8648,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8622,7 +8684,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="7" t="n">
+      <c r="G109" s="5" t="n">
         <v>1996</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8655,7 +8717,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N109" s="8" t="n">
+      <c r="N109" s="6" t="n">
         <v>2.577074097</v>
       </c>
       <c r="O109" s="4" t="inlineStr">
@@ -8665,7 +8727,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8701,7 +8763,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="7" t="n">
+      <c r="G110" s="5" t="n">
         <v>1997</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -8734,7 +8796,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N110" s="8" t="n">
+      <c r="N110" s="6" t="n">
         <v>4.652836296</v>
       </c>
       <c r="O110" s="4" t="inlineStr">
@@ -8744,7 +8806,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8780,7 +8842,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="7" t="n">
+      <c r="G111" s="5" t="n">
         <v>1998</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -8813,7 +8875,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N111" s="8" t="n">
+      <c r="N111" s="6" t="n">
         <v>8.550767856</v>
       </c>
       <c r="O111" s="4" t="inlineStr">
@@ -8823,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8859,7 +8921,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="7" t="n">
+      <c r="G112" s="5" t="n">
         <v>1999</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -8892,7 +8954,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N112" s="8" t="n">
+      <c r="N112" s="6" t="n">
         <v>15.79146876</v>
       </c>
       <c r="O112" s="4" t="inlineStr">
@@ -8902,7 +8964,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8938,7 +9000,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="7" t="n">
+      <c r="G113" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -8971,7 +9033,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N113" s="8" t="n">
+      <c r="N113" s="6" t="n">
         <v>22.2091444151412</v>
       </c>
       <c r="O113" s="4" t="inlineStr">
@@ -8981,7 +9043,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9017,7 +9079,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="7" t="n">
+      <c r="G114" s="5" t="n">
         <v>2001</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -9050,7 +9112,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N114" s="8" t="n">
+      <c r="N114" s="6" t="n">
         <v>25.9111457593823</v>
       </c>
       <c r="O114" s="4" t="inlineStr">
@@ -9060,7 +9122,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9096,7 +9158,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="7" t="n">
+      <c r="G115" s="5" t="n">
         <v>2002</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9129,7 +9191,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N115" s="8" t="n">
+      <c r="N115" s="6" t="n">
         <v>25.7193686771621</v>
       </c>
       <c r="O115" s="4" t="inlineStr">
@@ -9139,7 +9201,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9175,7 +9237,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="7" t="n">
+      <c r="G116" s="5" t="n">
         <v>2003</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9208,7 +9270,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N116" s="8" t="n">
+      <c r="N116" s="6" t="n">
         <v>27.0930423911324</v>
       </c>
       <c r="O116" s="4" t="inlineStr">
@@ -9218,7 +9280,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9254,7 +9316,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="7" t="n">
+      <c r="G117" s="5" t="n">
         <v>2004</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9287,7 +9349,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N117" s="8" t="n">
+      <c r="N117" s="6" t="n">
         <v>31.9692942191133</v>
       </c>
       <c r="O117" s="4" t="inlineStr">
@@ -9297,7 +9359,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9333,7 +9395,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="7" t="n">
+      <c r="G118" s="5" t="n">
         <v>2005</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9366,7 +9428,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N118" s="8" t="n">
+      <c r="N118" s="6" t="n">
         <v>46.6505354851398</v>
       </c>
       <c r="O118" s="4" t="inlineStr">
@@ -9376,7 +9438,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9412,7 +9474,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="7" t="n">
+      <c r="G119" s="5" t="n">
         <v>2006</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9445,7 +9507,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N119" s="8" t="n">
+      <c r="N119" s="6" t="n">
         <v>69.0162817672167</v>
       </c>
       <c r="O119" s="4" t="inlineStr">
@@ -9455,7 +9517,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9491,7 +9553,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="7" t="n">
+      <c r="G120" s="5" t="n">
         <v>2007</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9524,7 +9586,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N120" s="8" t="n">
+      <c r="N120" s="6" t="n">
         <v>86.15074784905531</v>
       </c>
       <c r="O120" s="4" t="inlineStr">
@@ -9534,7 +9596,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9570,7 +9632,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="7" t="n">
+      <c r="G121" s="5" t="n">
         <v>2008</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9603,7 +9665,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N121" s="8" t="n">
+      <c r="N121" s="6" t="n">
         <v>97.7210881589364</v>
       </c>
       <c r="O121" s="4" t="inlineStr">
@@ -9613,7 +9675,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9649,7 +9711,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="7" t="n">
+      <c r="G122" s="5" t="n">
         <v>2009</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9682,7 +9744,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N122" s="8" t="n">
+      <c r="N122" s="6" t="n">
         <v>98.89329523166261</v>
       </c>
       <c r="O122" s="4" t="inlineStr">
@@ -9692,7 +9754,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9728,7 +9790,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="7" t="n">
+      <c r="G123" s="5" t="n">
         <v>2010</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -9761,7 +9823,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N123" s="8" t="n">
+      <c r="N123" s="6" t="n">
         <v>96.76199725951049</v>
       </c>
       <c r="O123" s="4" t="inlineStr">
@@ -9771,7 +9833,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9807,7 +9869,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="7" t="n">
+      <c r="G124" s="5" t="n">
         <v>2011</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -9840,7 +9902,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N124" s="8" t="n">
+      <c r="N124" s="6" t="n">
         <v>98.6184338835709</v>
       </c>
       <c r="O124" s="4" t="inlineStr">
@@ -9850,7 +9912,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9886,7 +9948,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="7" t="n">
+      <c r="G125" s="5" t="n">
         <v>2012</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -9919,7 +9981,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N125" s="8" t="n">
+      <c r="N125" s="6" t="n">
         <v>103.435247267139</v>
       </c>
       <c r="O125" s="4" t="inlineStr">
@@ -9929,7 +9991,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9965,7 +10027,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="7" t="n">
+      <c r="G126" s="5" t="n">
         <v>2013</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -9998,7 +10060,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N126" s="8" t="n">
+      <c r="N126" s="6" t="n">
         <v>103.28923003251</v>
       </c>
       <c r="O126" s="4" t="inlineStr">
@@ -10008,7 +10070,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10044,7 +10106,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="7" t="n">
+      <c r="G127" s="5" t="n">
         <v>2014</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10077,7 +10139,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N127" s="8" t="n">
+      <c r="N127" s="6" t="n">
         <v>100.905474597326</v>
       </c>
       <c r="O127" s="4" t="inlineStr">
@@ -10087,7 +10149,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10123,7 +10185,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="7" t="n">
+      <c r="G128" s="5" t="n">
         <v>2015</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10156,7 +10218,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N128" s="8" t="n">
+      <c r="N128" s="6" t="n">
         <v>95.15779304043321</v>
       </c>
       <c r="O128" s="4" t="inlineStr">
@@ -10166,7 +10228,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10202,7 +10264,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="7" t="n">
+      <c r="G129" s="5" t="n">
         <v>2016</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10235,7 +10297,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N129" s="8" t="n">
+      <c r="N129" s="6" t="n">
         <v>89.713138519105</v>
       </c>
       <c r="O129" s="4" t="inlineStr">
@@ -10245,7 +10307,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10281,7 +10343,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="7" t="n">
+      <c r="G130" s="5" t="n">
         <v>2017</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10314,7 +10376,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N130" s="8" t="n">
+      <c r="N130" s="6" t="n">
         <v>80.1355411817503</v>
       </c>
       <c r="O130" s="4" t="inlineStr">
@@ -10324,7 +10386,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10360,7 +10422,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="7" t="n">
+      <c r="G131" s="5" t="n">
         <v>2018</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10393,7 +10455,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N131" s="8" t="n">
+      <c r="N131" s="6" t="n">
         <v>69.54996230490541</v>
       </c>
       <c r="O131" s="4" t="inlineStr">
@@ -10403,7 +10465,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10439,7 +10501,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="7" t="n">
+      <c r="G132" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10472,7 +10534,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N132" s="8" t="n">
+      <c r="N132" s="6" t="n">
         <v>63.8474442929871</v>
       </c>
       <c r="O132" s="4" t="inlineStr">
@@ -10482,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10518,7 +10580,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="7" t="n">
+      <c r="G133" s="5" t="n">
         <v>2020</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10551,7 +10613,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N133" s="8" t="n">
+      <c r="N133" s="6" t="n">
         <v>58.1625657953324</v>
       </c>
       <c r="O133" s="4" t="inlineStr">
@@ -10561,7 +10623,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10597,7 +10659,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="7" t="n">
+      <c r="G134" s="5" t="n">
         <v>2021</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10630,7 +10692,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N134" s="8" t="n">
+      <c r="N134" s="6" t="n">
         <v>60.2344883065715</v>
       </c>
       <c r="O134" s="4" t="inlineStr">
@@ -10640,7 +10702,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10676,7 +10738,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="7" t="n">
+      <c r="G135" s="5" t="n">
         <v>2022</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -10709,7 +10771,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N135" s="8" t="n">
+      <c r="N135" s="6" t="n">
         <v>66.4667731210739</v>
       </c>
       <c r="O135" s="4" t="inlineStr">
@@ -10719,7 +10781,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10755,7 +10817,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="7" t="n">
+      <c r="G136" s="5" t="n">
         <v>2023</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -10788,7 +10850,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N136" s="8" t="n">
+      <c r="N136" s="6" t="n">
         <v>70.2197325918151</v>
       </c>
       <c r="O136" s="4" t="inlineStr">
@@ -10798,7 +10860,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10834,7 +10896,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="7" t="n">
+      <c r="G137" s="5" t="n">
         <v>2024</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -10867,7 +10929,7 @@
           <t>Suscripciones móviles por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N137" s="8" t="n">
+      <c r="N137" s="6" t="n">
         <v>71.00759172250289</v>
       </c>
       <c r="O137" s="4" t="inlineStr">
@@ -10877,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10913,7 +10975,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="7" t="n">
+      <c r="G138" s="5" t="n">
         <v>2025</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -10954,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10990,7 +11052,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="7" t="n">
+      <c r="G139" s="5" t="n">
         <v>1960</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -11031,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11067,7 +11129,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="7" t="n">
+      <c r="G140" s="5" t="n">
         <v>1961</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -11108,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11144,7 +11206,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="7" t="n">
+      <c r="G141" s="5" t="n">
         <v>1962</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -11185,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11221,7 +11283,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="7" t="n">
+      <c r="G142" s="5" t="n">
         <v>1963</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -11262,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11298,7 +11360,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="7" t="n">
+      <c r="G143" s="5" t="n">
         <v>1964</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -11339,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11375,7 +11437,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="7" t="n">
+      <c r="G144" s="5" t="n">
         <v>1965</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -11416,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11452,7 +11514,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="7" t="n">
+      <c r="G145" s="5" t="n">
         <v>1966</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -11493,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11529,7 +11591,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="7" t="n">
+      <c r="G146" s="5" t="n">
         <v>1967</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -11570,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11606,7 +11668,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="7" t="n">
+      <c r="G147" s="5" t="n">
         <v>1968</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -11647,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11683,7 +11745,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="7" t="n">
+      <c r="G148" s="5" t="n">
         <v>1969</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -11724,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11760,7 +11822,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="7" t="n">
+      <c r="G149" s="5" t="n">
         <v>1970</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -11801,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11837,7 +11899,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="7" t="n">
+      <c r="G150" s="5" t="n">
         <v>1971</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -11878,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11914,7 +11976,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="7" t="n">
+      <c r="G151" s="5" t="n">
         <v>1972</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -11955,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11991,7 +12053,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="7" t="n">
+      <c r="G152" s="5" t="n">
         <v>1973</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -12032,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12068,7 +12130,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="7" t="n">
+      <c r="G153" s="5" t="n">
         <v>1974</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -12109,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12145,7 +12207,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="7" t="n">
+      <c r="G154" s="5" t="n">
         <v>1975</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -12186,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12222,7 +12284,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="7" t="n">
+      <c r="G155" s="5" t="n">
         <v>1976</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -12263,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12299,7 +12361,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="7" t="n">
+      <c r="G156" s="5" t="n">
         <v>1977</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -12340,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12376,7 +12438,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="7" t="n">
+      <c r="G157" s="5" t="n">
         <v>1978</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
@@ -12417,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12453,7 +12515,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="7" t="n">
+      <c r="G158" s="5" t="n">
         <v>1979</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
@@ -12494,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12530,7 +12592,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="7" t="n">
+      <c r="G159" s="5" t="n">
         <v>1980</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
@@ -12571,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12607,7 +12669,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="7" t="n">
+      <c r="G160" s="5" t="n">
         <v>1981</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -12648,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12684,7 +12746,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="7" t="n">
+      <c r="G161" s="5" t="n">
         <v>1982</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -12725,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12761,7 +12823,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="7" t="n">
+      <c r="G162" s="5" t="n">
         <v>1983</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -12802,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12838,7 +12900,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="7" t="n">
+      <c r="G163" s="5" t="n">
         <v>1984</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -12879,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12915,7 +12977,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="7" t="n">
+      <c r="G164" s="5" t="n">
         <v>1985</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -12956,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12992,7 +13054,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="7" t="n">
+      <c r="G165" s="5" t="n">
         <v>1986</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -13033,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13069,7 +13131,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="7" t="n">
+      <c r="G166" s="5" t="n">
         <v>1987</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -13110,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13146,7 +13208,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="7" t="n">
+      <c r="G167" s="5" t="n">
         <v>1988</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -13187,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13223,7 +13285,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="7" t="n">
+      <c r="G168" s="5" t="n">
         <v>1989</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -13264,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13300,7 +13362,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="7" t="n">
+      <c r="G169" s="5" t="n">
         <v>1990</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -13341,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13377,7 +13439,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="7" t="n">
+      <c r="G170" s="5" t="n">
         <v>1991</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -13418,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13454,7 +13516,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="7" t="n">
+      <c r="G171" s="5" t="n">
         <v>1992</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -13495,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13531,7 +13593,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="7" t="n">
+      <c r="G172" s="5" t="n">
         <v>1993</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -13572,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13608,7 +13670,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="7" t="n">
+      <c r="G173" s="5" t="n">
         <v>1994</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -13649,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13685,7 +13747,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="7" t="n">
+      <c r="G174" s="5" t="n">
         <v>1995</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -13726,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13762,7 +13824,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="7" t="n">
+      <c r="G175" s="5" t="n">
         <v>1996</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -13803,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13839,7 +13901,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="7" t="n">
+      <c r="G176" s="5" t="n">
         <v>1997</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -13880,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13916,7 +13978,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="7" t="n">
+      <c r="G177" s="5" t="n">
         <v>1998</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -13957,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13993,7 +14055,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="7" t="n">
+      <c r="G178" s="5" t="n">
         <v>1999</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -14034,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14070,7 +14132,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="7" t="n">
+      <c r="G179" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -14103,7 +14165,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N179" s="8" t="n">
+      <c r="N179" s="6" t="n">
         <v>0.0182372620084196</v>
       </c>
       <c r="O179" s="4" t="inlineStr">
@@ -14113,7 +14175,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14149,7 +14211,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="7" t="n">
+      <c r="G180" s="5" t="n">
         <v>2001</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -14182,7 +14244,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N180" s="8" t="n">
+      <c r="N180" s="6" t="n">
         <v>0.146661787014387</v>
       </c>
       <c r="O180" s="4" t="inlineStr">
@@ -14192,7 +14254,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14228,7 +14290,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="7" t="n">
+      <c r="G181" s="5" t="n">
         <v>2002</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -14261,7 +14323,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N181" s="8" t="n">
+      <c r="N181" s="6" t="n">
         <v>0.307249610202931</v>
       </c>
       <c r="O181" s="4" t="inlineStr">
@@ -14271,7 +14333,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14307,7 +14369,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="7" t="n">
+      <c r="G182" s="5" t="n">
         <v>2003</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -14340,7 +14402,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N182" s="8" t="n">
+      <c r="N182" s="6" t="n">
         <v>0.451853172687301</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
@@ -14350,7 +14412,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14386,7 +14448,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="7" t="n">
+      <c r="G183" s="5" t="n">
         <v>2004</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -14419,7 +14481,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N183" s="8" t="n">
+      <c r="N183" s="6" t="n">
         <v>0.798034595558425</v>
       </c>
       <c r="O183" s="4" t="inlineStr">
@@ -14429,7 +14491,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14465,7 +14527,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="7" t="n">
+      <c r="G184" s="5" t="n">
         <v>2005</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -14498,7 +14560,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N184" s="8" t="n">
+      <c r="N184" s="6" t="n">
         <v>1.32980141271847</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
@@ -14508,7 +14570,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14544,7 +14606,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="7" t="n">
+      <c r="G185" s="5" t="n">
         <v>2006</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -14577,7 +14639,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N185" s="8" t="n">
+      <c r="N185" s="6" t="n">
         <v>1.97478127020455</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
@@ -14587,7 +14649,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14623,7 +14685,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="7" t="n">
+      <c r="G186" s="5" t="n">
         <v>2007</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -14656,7 +14718,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N186" s="8" t="n">
+      <c r="N186" s="6" t="n">
         <v>3.10246568790753</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
@@ -14666,7 +14728,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14702,7 +14764,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="7" t="n">
+      <c r="G187" s="5" t="n">
         <v>2008</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -14735,7 +14797,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N187" s="8" t="n">
+      <c r="N187" s="6" t="n">
         <v>3.97495217742432</v>
       </c>
       <c r="O187" s="4" t="inlineStr">
@@ -14745,7 +14807,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14781,7 +14843,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="7" t="n">
+      <c r="G188" s="5" t="n">
         <v>2009</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -14814,7 +14876,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N188" s="8" t="n">
+      <c r="N188" s="6" t="n">
         <v>4.92838214157542</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
@@ -14824,7 +14886,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14860,7 +14922,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="7" t="n">
+      <c r="G189" s="5" t="n">
         <v>2010</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -14893,7 +14955,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N189" s="8" t="n">
+      <c r="N189" s="6" t="n">
         <v>5.80665024566429</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
@@ -14903,7 +14965,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14939,7 +15001,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="7" t="n">
+      <c r="G190" s="5" t="n">
         <v>2011</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -14972,7 +15034,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N190" s="8" t="n">
+      <c r="N190" s="6" t="n">
         <v>6.22108895422792</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
@@ -14982,7 +15044,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15018,7 +15080,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="7" t="n">
+      <c r="G191" s="5" t="n">
         <v>2012</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -15051,7 +15113,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N191" s="8" t="n">
+      <c r="N191" s="6" t="n">
         <v>6.89152396038334</v>
       </c>
       <c r="O191" s="4" t="inlineStr">
@@ -15061,7 +15123,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15097,7 +15159,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="7" t="n">
+      <c r="G192" s="5" t="n">
         <v>2013</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -15130,7 +15192,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N192" s="8" t="n">
+      <c r="N192" s="6" t="n">
         <v>7.4666228138768</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
@@ -15140,7 +15202,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15176,7 +15238,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="7" t="n">
+      <c r="G193" s="5" t="n">
         <v>2014</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -15209,7 +15271,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N193" s="8" t="n">
+      <c r="N193" s="6" t="n">
         <v>7.9330889563685</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
@@ -15219,7 +15281,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15255,7 +15317,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="7" t="n">
+      <c r="G194" s="5" t="n">
         <v>2015</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -15288,7 +15350,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N194" s="8" t="n">
+      <c r="N194" s="6" t="n">
         <v>8.470319132888591</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
@@ -15298,7 +15360,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15334,7 +15396,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="7" t="n">
+      <c r="G195" s="5" t="n">
         <v>2016</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -15367,7 +15429,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N195" s="8" t="n">
+      <c r="N195" s="6" t="n">
         <v>8.496440193826119</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
@@ -15377,7 +15439,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15413,7 +15475,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="7" t="n">
+      <c r="G196" s="5" t="n">
         <v>2017</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -15446,7 +15508,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N196" s="8" t="n">
+      <c r="N196" s="6" t="n">
         <v>8.531985740834481</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
@@ -15456,7 +15518,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15492,7 +15554,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="7" t="n">
+      <c r="G197" s="5" t="n">
         <v>2018</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -15525,7 +15587,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N197" s="8" t="n">
+      <c r="N197" s="6" t="n">
         <v>8.737968501447551</v>
       </c>
       <c r="O197" s="4" t="inlineStr">
@@ -15535,7 +15597,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15571,7 +15633,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="7" t="n">
+      <c r="G198" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -15604,7 +15666,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N198" s="8" t="n">
+      <c r="N198" s="6" t="n">
         <v>8.850374340428321</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
@@ -15614,7 +15676,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15650,7 +15712,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="7" t="n">
+      <c r="G199" s="5" t="n">
         <v>2020</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -15683,7 +15745,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N199" s="8" t="n">
+      <c r="N199" s="6" t="n">
         <v>9.00606477756336</v>
       </c>
       <c r="O199" s="4" t="inlineStr">
@@ -15693,7 +15755,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15729,7 +15791,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="7" t="n">
+      <c r="G200" s="5" t="n">
         <v>2021</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -15762,7 +15824,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N200" s="8" t="n">
+      <c r="N200" s="6" t="n">
         <v>9.2424360147272</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
@@ -15772,7 +15834,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15808,7 +15870,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="7" t="n">
+      <c r="G201" s="5" t="n">
         <v>2022</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -15841,7 +15903,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N201" s="8" t="n">
+      <c r="N201" s="6" t="n">
         <v>9.580361433872881</v>
       </c>
       <c r="O201" s="4" t="inlineStr">
@@ -15851,7 +15913,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15887,7 +15949,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="7" t="n">
+      <c r="G202" s="5" t="n">
         <v>2023</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -15920,7 +15982,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N202" s="8" t="n">
+      <c r="N202" s="6" t="n">
         <v>10.638053537183</v>
       </c>
       <c r="O202" s="4" t="inlineStr">
@@ -15930,7 +15992,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15966,7 +16028,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="7" t="n">
+      <c r="G203" s="5" t="n">
         <v>2024</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
@@ -15999,7 +16061,7 @@
           <t>Suscripciones de banda ancha fija por cada 100 habitantes</t>
         </is>
       </c>
-      <c r="N203" s="8" t="n">
+      <c r="N203" s="6" t="n">
         <v>12.9446636524427</v>
       </c>
       <c r="O203" s="4" t="inlineStr">
@@ -16009,7 +16071,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16045,7 +16107,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="7" t="n">
+      <c r="G204" s="5" t="n">
         <v>2025</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -16086,7 +16148,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16122,7 +16184,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="7" t="n">
+      <c r="G205" s="5" t="n">
         <v>1960</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -16163,7 +16225,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16199,7 +16261,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="7" t="n">
+      <c r="G206" s="5" t="n">
         <v>1961</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -16240,7 +16302,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16276,7 +16338,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="7" t="n">
+      <c r="G207" s="5" t="n">
         <v>1962</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
@@ -16317,7 +16379,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16353,7 +16415,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="7" t="n">
+      <c r="G208" s="5" t="n">
         <v>1963</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -16394,7 +16456,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16430,7 +16492,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="7" t="n">
+      <c r="G209" s="5" t="n">
         <v>1964</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -16471,7 +16533,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16507,7 +16569,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="7" t="n">
+      <c r="G210" s="5" t="n">
         <v>1965</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -16548,7 +16610,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16584,7 +16646,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="7" t="n">
+      <c r="G211" s="5" t="n">
         <v>1966</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -16625,7 +16687,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16661,7 +16723,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="7" t="n">
+      <c r="G212" s="5" t="n">
         <v>1967</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -16702,7 +16764,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16738,7 +16800,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="7" t="n">
+      <c r="G213" s="5" t="n">
         <v>1968</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -16779,7 +16841,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16815,7 +16877,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="7" t="n">
+      <c r="G214" s="5" t="n">
         <v>1969</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -16856,7 +16918,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16892,7 +16954,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="7" t="n">
+      <c r="G215" s="5" t="n">
         <v>1970</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -16933,7 +16995,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16969,7 +17031,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="7" t="n">
+      <c r="G216" s="5" t="n">
         <v>1971</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
@@ -17010,7 +17072,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17046,7 +17108,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="7" t="n">
+      <c r="G217" s="5" t="n">
         <v>1972</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
@@ -17087,7 +17149,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17123,7 +17185,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="7" t="n">
+      <c r="G218" s="5" t="n">
         <v>1973</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -17164,7 +17226,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17200,7 +17262,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="7" t="n">
+      <c r="G219" s="5" t="n">
         <v>1974</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -17241,7 +17303,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17277,7 +17339,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="7" t="n">
+      <c r="G220" s="5" t="n">
         <v>1975</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -17318,7 +17380,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17354,7 +17416,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="7" t="n">
+      <c r="G221" s="5" t="n">
         <v>1976</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -17395,7 +17457,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17431,7 +17493,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="7" t="n">
+      <c r="G222" s="5" t="n">
         <v>1977</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -17472,7 +17534,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17508,7 +17570,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="7" t="n">
+      <c r="G223" s="5" t="n">
         <v>1978</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -17549,7 +17611,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17585,7 +17647,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="7" t="n">
+      <c r="G224" s="5" t="n">
         <v>1979</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -17626,7 +17688,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17662,7 +17724,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="7" t="n">
+      <c r="G225" s="5" t="n">
         <v>1980</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -17703,7 +17765,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17739,7 +17801,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="7" t="n">
+      <c r="G226" s="5" t="n">
         <v>1981</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -17780,7 +17842,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17816,7 +17878,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="7" t="n">
+      <c r="G227" s="5" t="n">
         <v>1982</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -17857,7 +17919,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17893,7 +17955,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="7" t="n">
+      <c r="G228" s="5" t="n">
         <v>1983</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -17934,7 +17996,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17970,7 +18032,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="7" t="n">
+      <c r="G229" s="5" t="n">
         <v>1984</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
@@ -18011,7 +18073,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18047,7 +18109,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="7" t="n">
+      <c r="G230" s="5" t="n">
         <v>1985</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -18088,7 +18150,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18124,7 +18186,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="7" t="n">
+      <c r="G231" s="5" t="n">
         <v>1986</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
@@ -18165,7 +18227,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18201,7 +18263,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="7" t="n">
+      <c r="G232" s="5" t="n">
         <v>1987</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
@@ -18242,7 +18304,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18278,7 +18340,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="7" t="n">
+      <c r="G233" s="5" t="n">
         <v>1988</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
@@ -18319,7 +18381,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18355,7 +18417,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="7" t="n">
+      <c r="G234" s="5" t="n">
         <v>1989</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
@@ -18396,7 +18458,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18432,7 +18494,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="7" t="n">
+      <c r="G235" s="5" t="n">
         <v>1990</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -18465,7 +18527,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N235" s="7" t="n">
+      <c r="N235" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O235" s="4" t="inlineStr">
@@ -18475,7 +18537,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18511,7 +18573,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="7" t="n">
+      <c r="G236" s="5" t="n">
         <v>1991</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
@@ -18552,7 +18614,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18588,7 +18650,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="7" t="n">
+      <c r="G237" s="5" t="n">
         <v>1992</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -18621,7 +18683,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N237" s="8" t="n">
+      <c r="N237" s="6" t="n">
         <v>0.0121</v>
       </c>
       <c r="O237" s="4" t="inlineStr">
@@ -18631,7 +18693,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18667,7 +18729,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="7" t="n">
+      <c r="G238" s="5" t="n">
         <v>1993</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
@@ -18700,7 +18762,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N238" s="8" t="n">
+      <c r="N238" s="6" t="n">
         <v>0.0416</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
@@ -18710,7 +18772,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18746,7 +18808,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="7" t="n">
+      <c r="G239" s="5" t="n">
         <v>1994</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
@@ -18779,7 +18841,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N239" s="8" t="n">
+      <c r="N239" s="6" t="n">
         <v>0.0555</v>
       </c>
       <c r="O239" s="4" t="inlineStr">
@@ -18789,7 +18851,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18825,7 +18887,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="7" t="n">
+      <c r="G240" s="5" t="n">
         <v>1995</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
@@ -18858,7 +18920,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N240" s="8" t="n">
+      <c r="N240" s="6" t="n">
         <v>0.122</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
@@ -18868,7 +18930,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18904,7 +18966,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="7" t="n">
+      <c r="G241" s="5" t="n">
         <v>1996</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
@@ -18937,7 +18999,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N241" s="8" t="n">
+      <c r="N241" s="6" t="n">
         <v>0.248</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
@@ -18947,7 +19009,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18983,7 +19045,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="7" t="n">
+      <c r="G242" s="5" t="n">
         <v>1997</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
@@ -19016,7 +19078,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N242" s="8" t="n">
+      <c r="N242" s="6" t="n">
         <v>0.391</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
@@ -19026,7 +19088,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19062,7 +19124,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="7" t="n">
+      <c r="G243" s="5" t="n">
         <v>1998</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
@@ -19095,7 +19157,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N243" s="8" t="n">
+      <c r="N243" s="6" t="n">
         <v>1.38</v>
       </c>
       <c r="O243" s="4" t="inlineStr">
@@ -19105,7 +19167,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19141,7 +19203,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="7" t="n">
+      <c r="G244" s="5" t="n">
         <v>1999</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
@@ -19174,7 +19236,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N244" s="8" t="n">
+      <c r="N244" s="6" t="n">
         <v>2.84</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
@@ -19184,7 +19246,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19220,7 +19282,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="7" t="n">
+      <c r="G245" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -19253,7 +19315,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N245" s="8" t="n">
+      <c r="N245" s="6" t="n">
         <v>3.3595974645036</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
@@ -19263,7 +19325,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19299,7 +19361,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="7" t="n">
+      <c r="G246" s="5" t="n">
         <v>2001</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -19332,7 +19394,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N246" s="8" t="n">
+      <c r="N246" s="6" t="n">
         <v>4.63600094778677</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
@@ -19342,7 +19404,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19378,7 +19440,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="7" t="n">
+      <c r="G247" s="5" t="n">
         <v>2002</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -19411,7 +19473,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N247" s="8" t="n">
+      <c r="N247" s="6" t="n">
         <v>4.91044632720325</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
@@ -19421,7 +19483,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19457,7 +19519,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="7" t="n">
+      <c r="G248" s="5" t="n">
         <v>2003</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -19490,7 +19552,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N248" s="8" t="n">
+      <c r="N248" s="6" t="n">
         <v>7.49996346522407</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
@@ -19500,7 +19562,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19536,7 +19598,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="7" t="n">
+      <c r="G249" s="5" t="n">
         <v>2004</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -19569,7 +19631,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N249" s="8" t="n">
+      <c r="N249" s="6" t="n">
         <v>8.40446959241215</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
@@ -19579,7 +19641,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19615,7 +19677,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="7" t="n">
+      <c r="G250" s="5" t="n">
         <v>2005</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -19648,7 +19710,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N250" s="8" t="n">
+      <c r="N250" s="6" t="n">
         <v>12.5529979098299</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
@@ -19658,7 +19720,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19694,7 +19756,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="7" t="n">
+      <c r="G251" s="5" t="n">
         <v>2006</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -19727,7 +19789,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N251" s="8" t="n">
+      <c r="N251" s="6" t="n">
         <v>15.2247114771787</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
@@ -19737,7 +19799,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19773,7 +19835,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="7" t="n">
+      <c r="G252" s="5" t="n">
         <v>2007</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -19806,7 +19868,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N252" s="8" t="n">
+      <c r="N252" s="6" t="n">
         <v>20.83</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
@@ -19816,7 +19878,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19852,7 +19914,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="7" t="n">
+      <c r="G253" s="5" t="n">
         <v>2008</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -19885,7 +19947,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N253" s="8" t="n">
+      <c r="N253" s="6" t="n">
         <v>25.88</v>
       </c>
       <c r="O253" s="4" t="inlineStr">
@@ -19895,7 +19957,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19931,7 +19993,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="7" t="n">
+      <c r="G254" s="5" t="n">
         <v>2009</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -19964,7 +20026,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N254" s="8" t="n">
+      <c r="N254" s="6" t="n">
         <v>32.7</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
@@ -19974,7 +20036,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20010,7 +20072,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="7" t="n">
+      <c r="G255" s="5" t="n">
         <v>2010</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -20043,7 +20105,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N255" s="8" t="n">
+      <c r="N255" s="6" t="n">
         <v>37.37</v>
       </c>
       <c r="O255" s="4" t="inlineStr">
@@ -20053,7 +20115,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20089,7 +20151,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="7" t="n">
+      <c r="G256" s="5" t="n">
         <v>2011</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
@@ -20122,7 +20184,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N256" s="8" t="n">
+      <c r="N256" s="6" t="n">
         <v>40.22</v>
       </c>
       <c r="O256" s="4" t="inlineStr">
@@ -20132,7 +20194,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20168,7 +20230,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="7" t="n">
+      <c r="G257" s="5" t="n">
         <v>2012</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
@@ -20201,7 +20263,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N257" s="8" t="n">
+      <c r="N257" s="6" t="n">
         <v>49.0500830729861</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
@@ -20211,7 +20273,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20247,7 +20309,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="7" t="n">
+      <c r="G258" s="5" t="n">
         <v>2013</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
@@ -20280,7 +20342,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N258" s="8" t="n">
+      <c r="N258" s="6" t="n">
         <v>54.90000153</v>
       </c>
       <c r="O258" s="4" t="inlineStr">
@@ -20290,7 +20352,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20326,7 +20388,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="7" t="n">
+      <c r="G259" s="5" t="n">
         <v>2014</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
@@ -20359,7 +20421,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N259" s="7" t="n">
+      <c r="N259" s="5" t="n">
         <v>57</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
@@ -20369,7 +20431,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20405,7 +20467,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="7" t="n">
+      <c r="G260" s="5" t="n">
         <v>2015</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
@@ -20438,7 +20500,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N260" s="7" t="n">
+      <c r="N260" s="5" t="n">
         <v>58</v>
       </c>
       <c r="O260" s="4" t="inlineStr">
@@ -20448,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20484,7 +20546,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="7" t="n">
+      <c r="G261" s="5" t="n">
         <v>2016</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
@@ -20517,7 +20579,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N261" s="7" t="n">
+      <c r="N261" s="5" t="n">
         <v>60</v>
       </c>
       <c r="O261" s="4" t="inlineStr">
@@ -20527,7 +20589,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20563,7 +20625,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="7" t="n">
+      <c r="G262" s="5" t="n">
         <v>2017</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
@@ -20604,7 +20666,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20640,7 +20702,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="7" t="n">
+      <c r="G263" s="5" t="n">
         <v>2018</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
@@ -20681,7 +20743,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20717,7 +20779,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="7" t="n">
+      <c r="G264" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
@@ -20750,7 +20812,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N264" s="8" t="n">
+      <c r="N264" s="6" t="n">
         <v>49.05009842</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
@@ -20760,7 +20822,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20796,7 +20858,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="7" t="n">
+      <c r="G265" s="5" t="n">
         <v>2020</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
@@ -20829,7 +20891,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N265" s="8" t="n">
+      <c r="N265" s="6" t="n">
         <v>72.44110107</v>
       </c>
       <c r="O265" s="4" t="inlineStr">
@@ -20839,7 +20901,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20875,7 +20937,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="7" t="n">
+      <c r="G266" s="5" t="n">
         <v>2021</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
@@ -20908,7 +20970,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N266" s="8" t="n">
+      <c r="N266" s="6" t="n">
         <v>74.11219788</v>
       </c>
       <c r="O266" s="4" t="inlineStr">
@@ -20918,7 +20980,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20954,7 +21016,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="7" t="n">
+      <c r="G267" s="5" t="n">
         <v>2022</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
@@ -20987,7 +21049,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N267" s="8" t="n">
+      <c r="N267" s="6" t="n">
         <v>75.82180022999999</v>
       </c>
       <c r="O267" s="4" t="inlineStr">
@@ -20997,7 +21059,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21033,7 +21095,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="7" t="n">
+      <c r="G268" s="5" t="n">
         <v>2023</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
@@ -21066,7 +21128,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N268" s="8" t="n">
+      <c r="N268" s="6" t="n">
         <v>76.33190155</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
@@ -21076,7 +21138,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21112,7 +21174,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="7" t="n">
+      <c r="G269" s="5" t="n">
         <v>2024</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
@@ -21145,7 +21207,7 @@
           <t>Usuarios de internet como porcentaje de la población</t>
         </is>
       </c>
-      <c r="N269" s="8" t="n">
+      <c r="N269" s="6" t="n">
         <v>76.67890167</v>
       </c>
       <c r="O269" s="4" t="inlineStr">
@@ -21155,7 +21217,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21191,7 +21253,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="7" t="n">
+      <c r="G270" s="5" t="n">
         <v>2025</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
@@ -21232,7 +21294,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21266,7 +21328,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Banco Mundial - Venezuela - Infraestructura y digitalización</t>
+          <t>Banco Mundial - Infraestructura y digitalización</t>
         </is>
       </c>
     </row>
@@ -21274,19 +21336,19 @@
     <row r="4" ht="16" customHeight="1"/>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Campo</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Organización</t>
         </is>
@@ -21298,7 +21360,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
@@ -21310,34 +21372,34 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Fecha generación</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="5" t="n">
         <v>264</v>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15755,7 +15755,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17380,7 +17380,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17611,7 +17611,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19167,7 +19167,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15755,7 +15755,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17380,7 +17380,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17611,7 +17611,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19167,7 +19167,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15755,7 +15755,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17380,7 +17380,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17611,7 +17611,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19167,7 +19167,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15755,7 +15755,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17380,7 +17380,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17611,7 +17611,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19167,7 +19167,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15755,7 +15755,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17380,7 +17380,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17611,7 +17611,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19167,7 +19167,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
